--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44753</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>44972</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45558</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45636</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>44972</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44838</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44494</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44881</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>45625</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44972</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>45734</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44522</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>45295</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45716</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>45636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45399</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44474</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46258</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45770</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45399</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45051</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>46073</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45903</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46270</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44657</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45349</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         <v>45208</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45399</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>46275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8525,7 +8525,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45463</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>46058</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>45238</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>46255</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45625</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>44735</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45490</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>44888</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45478</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45764</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45497</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44648</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45573</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45589</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>44972</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>44515</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11915,7 +11915,7 @@
         <v>45665</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45799</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45709</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>46076</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12837,7 +12837,7 @@
         <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>46009</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45461</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44515</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45961</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45618</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>45278</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45113</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>46255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>45730</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45558</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45561</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45399</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>44529</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>44806</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45478</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45560</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45487</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>46062</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>46093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>46085</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44603</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>45733</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45643</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45461</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45119</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>44518</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>45937</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>46148</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45545</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45625</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45618</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17131,7 +17131,7 @@
         <v>46003</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45560</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45636</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44985</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46252</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>45541</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>46268</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45492</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45751</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>46048</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>46162</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18334,7 +18334,7 @@
         <v>45817</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>45834</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45883</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45895</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>46093</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44518</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>44532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>44852</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45526</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45105</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45240</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45206</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45117</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>44911</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>45515</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45736</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>44494</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45541</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44560</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>46072</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45540</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45586</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20969,7 +20969,7 @@
         <v>46163</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45523</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>45936</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45254</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45573</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>46210</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45399</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>46097</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45589</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45804</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45821</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>45874</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45439</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45469</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
         <v>46247</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>44812</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44628</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44619</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44619</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>44810</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23745,7 +23745,7 @@
         <v>44867</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44533</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44628</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44852</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>44712</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44619</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>44817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44532</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44690</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44858</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44889</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44743</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>44754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44619</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>44616</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>44482</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44755</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>44532</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44852</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>44743</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25504,7 +25504,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44462</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44708</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>44532</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44805</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>44879</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>44799</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44617</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44545</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44495</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>44837</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>44743</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45471</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         <v>45597</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45481</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44459</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>44545</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>44914</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>45660</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45470</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45643</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>45140</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45048</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27336,7 +27336,7 @@
         <v>44657</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>45518</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45190</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27560,7 +27560,7 @@
         <v>44972</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45254</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45541</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45000</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27940,7 +27940,7 @@
         <v>45560</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>44889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>44627</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45478</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45571</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>45571</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45237</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44942</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>45238</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45693</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44923</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44522</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44515</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>45166</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45114</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44748</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45202</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29377,7 +29377,7 @@
         <v>45512</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29455,7 +29455,7 @@
         <v>45545</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>45555</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29606,7 +29606,7 @@
         <v>45531</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45239</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44802</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>45730</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45730</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29991,7 +29991,7 @@
         <v>45573</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>45526</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30142,7 +30142,7 @@
         <v>45526</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>44971</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30293,7 +30293,7 @@
         <v>45656</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45469</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45232</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>44568</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30595,7 +30595,7 @@
         <v>45338</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45195</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45597</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45238</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45238</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>44852</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45239</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>45308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45259</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>44515</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>44515</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45579</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>44847</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>44522</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44826</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45730</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45730</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45240</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32032,7 +32032,7 @@
         <v>45463</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32110,7 +32110,7 @@
         <v>44505</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45636</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45656</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45730</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32417,7 +32417,7 @@
         <v>45730</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32495,7 +32495,7 @@
         <v>45590</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32568,7 +32568,7 @@
         <v>44847</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32641,7 +32641,7 @@
         <v>45463</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45161</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>45280</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45618</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32948,7 +32948,7 @@
         <v>45226</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45495</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33104,7 +33104,7 @@
         <v>45343</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>45769</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>44981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45170</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45735</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45884</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33557,7 +33557,7 @@
         <v>45216</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45483</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>44543</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45847</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44963</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45505</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>44855</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45587</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>45890</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>45890</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34395,7 +34395,7 @@
         <v>45884</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>44540</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45890</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34624,7 +34624,7 @@
         <v>45890</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>45884</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45125</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45161</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45408</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>44890</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45757</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44488</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>45403</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45388</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35447,7 +35447,7 @@
         <v>44972</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>45659</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>45915</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>45915</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>45692</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45558</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45636</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45574</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45775</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36129,7 +36129,7 @@
         <v>45546</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36202,7 +36202,7 @@
         <v>45238</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36280,7 +36280,7 @@
         <v>45642</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45089</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45399</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>44957</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45331</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>44977</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>46144</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45415</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45229</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>44515</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45937</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45636</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45643</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>45636</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>45142</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37483,7 +37483,7 @@
         <v>45636</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37561,7 +37561,7 @@
         <v>45435</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37717,7 +37717,7 @@
         <v>45944</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45216</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>46149</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>44972</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38029,7 +38029,7 @@
         <v>45951</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45161</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45951</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>46153</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45715</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>44658</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38555,7 +38555,7 @@
         <v>45954</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45954</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>45957</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45636</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>44847</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44847</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>46150</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45762</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45754</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45558</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>45508</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45957</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>45957</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>45957</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45000</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>44917</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45957</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45957</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39977,7 +39977,7 @@
         <v>45957</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40050,7 +40050,7 @@
         <v>45957</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45957</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45957</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45957</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40342,7 +40342,7 @@
         <v>45478</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>45894</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>45636</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>45225</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>45971</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>44911</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45625</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>45195</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>44972</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45478</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41341,7 +41341,7 @@
         <v>45985</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>45982</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>44994</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>44623</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41648,7 +41648,7 @@
         <v>46157</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41726,7 +41726,7 @@
         <v>44943</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>46157</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45232</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44657</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45653</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>45436</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>46160</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45089</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42325,7 +42325,7 @@
         <v>45442</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45216</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45993</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>46048</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42627,7 +42627,7 @@
         <v>45993</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44545</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42773,7 +42773,7 @@
         <v>45478</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42851,7 +42851,7 @@
         <v>46162</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42924,7 +42924,7 @@
         <v>45435</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>46163</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45399</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>44545</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>45622</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45232</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45188</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>45428</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>46163</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>45996</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45996</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45574</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45457</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>45999</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>45582</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>45408</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>46001</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44283,7 +44283,7 @@
         <v>45453</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45443</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>45622</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>44881</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>46006</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44658,7 +44658,7 @@
         <v>45756</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44736,7 +44736,7 @@
         <v>45207</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45225</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44892,7 +44892,7 @@
         <v>46168</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>46168</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46168</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45126,7 +45126,7 @@
         <v>45148</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45205</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>44470</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45757</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>45236</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>44903</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45222</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45429</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45617</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>44637</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45475</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45552</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45297</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45526</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45636</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45246</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>46038</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>46174</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45545</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46174</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45152</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>46171</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>45148</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46963,7 +46963,7 @@
         <v>45511</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>46045</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47119,7 +47119,7 @@
         <v>45526</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         <v>46087</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47275,7 +47275,7 @@
         <v>46175</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45509</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>46055</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47504,7 +47504,7 @@
         <v>44532</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47577,7 +47577,7 @@
         <v>44995</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>46055</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47728,7 +47728,7 @@
         <v>46055</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>46055</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>45239</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>44881</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45625</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>46049</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48171,7 +48171,7 @@
         <v>45756</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>45756</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>45756</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48390,7 +48390,7 @@
         <v>45565</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48468,7 +48468,7 @@
         <v>44972</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45659</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46181</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>45659</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>45659</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>46066</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>46070</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>46183</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49067,7 +49067,7 @@
         <v>46183</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49140,7 +49140,7 @@
         <v>45159</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45190</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49291,7 +49291,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45297</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>46183</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49520,7 +49520,7 @@
         <v>44972</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49598,7 +49598,7 @@
         <v>46189</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49671,7 +49671,7 @@
         <v>45117</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>44628</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45485</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>45518</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45092</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45545</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45238</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45238</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50285,7 +50285,7 @@
         <v>45376</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50358,7 +50358,7 @@
         <v>45206</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>45225</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50514,7 +50514,7 @@
         <v>44522</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50592,7 +50592,7 @@
         <v>45084</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50670,7 +50670,7 @@
         <v>45154</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50748,7 +50748,7 @@
         <v>45492</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>45492</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50904,7 +50904,7 @@
         <v>45469</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>46093</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51060,7 +51060,7 @@
         <v>45777</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>46184</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>46191</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>46191</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51362,7 +51362,7 @@
         <v>45090</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>46196</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51518,7 +51518,7 @@
         <v>46196</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51596,7 +51596,7 @@
         <v>45912</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51669,7 +51669,7 @@
         <v>45541</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>46198</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51825,7 +51825,7 @@
         <v>46198</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51898,7 +51898,7 @@
         <v>46105</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51976,7 +51976,7 @@
         <v>45972</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>45972</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52122,7 +52122,7 @@
         <v>45152</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         <v>45236</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52273,7 +52273,7 @@
         <v>46198</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52351,7 +52351,7 @@
         <v>45450</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52429,7 +52429,7 @@
         <v>45278</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52502,7 +52502,7 @@
         <v>46198</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52580,7 +52580,7 @@
         <v>46111</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52658,7 +52658,7 @@
         <v>45756</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>46111</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>46244</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52892,7 +52892,7 @@
         <v>45748</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>46199</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53038,7 +53038,7 @@
         <v>44743</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53116,7 +53116,7 @@
         <v>46114</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53189,7 +53189,7 @@
         <v>46113</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>46113</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53345,7 +53345,7 @@
         <v>45709</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>46113</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>44972</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45931</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>44826</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45000</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>46122</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>46122</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>44943</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45300</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>46122</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>46121</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>44628</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54309,7 +54309,7 @@
         <v>45042</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54387,7 +54387,7 @@
         <v>46125</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54465,7 +54465,7 @@
         <v>45635</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54538,7 +54538,7 @@
         <v>45222</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54616,7 +54616,7 @@
         <v>46129</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         <v>46199</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54772,7 +54772,7 @@
         <v>44923</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>46132</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>46204</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>46132</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>46132</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>45419</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45524</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>46205</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>44564</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         <v>46129</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>44977</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55615,7 +55615,7 @@
         <v>44977</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45251</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45992</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55839,7 +55839,7 @@
         <v>45709</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>46204</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>46204</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>44857</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46204</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56219,7 +56219,7 @@
         <v>45349</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56292,7 +56292,7 @@
         <v>44615</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>45993</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56438,7 +56438,7 @@
         <v>46204</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>44735</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>44488</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>45453</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>45453</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56823,7 +56823,7 @@
         <v>46248</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56901,7 +56901,7 @@
         <v>45730</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56979,7 +56979,7 @@
         <v>45730</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57057,7 +57057,7 @@
         <v>46206</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57135,7 +57135,7 @@
         <v>45769</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57213,7 +57213,7 @@
         <v>46076</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57286,7 +57286,7 @@
         <v>46206</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>46205</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>46205</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>46205</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>45800</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57661,7 +57661,7 @@
         <v>46252</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45524</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45238</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57895,7 +57895,7 @@
         <v>45575</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57973,7 +57973,7 @@
         <v>45587</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>46252</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45520</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58202,7 +58202,7 @@
         <v>46252</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>46209</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58353,7 +58353,7 @@
         <v>46209</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>46210</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58504,7 +58504,7 @@
         <v>46209</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58582,7 +58582,7 @@
         <v>45583</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58660,7 +58660,7 @@
         <v>46210</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58733,7 +58733,7 @@
         <v>45254</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>46252</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>46209</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>46178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59040,7 +59040,7 @@
         <v>45589</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59118,7 +59118,7 @@
         <v>45743</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59191,7 +59191,7 @@
         <v>44903</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59264,7 +59264,7 @@
         <v>46252</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59337,7 +59337,7 @@
         <v>46209</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>46252</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>46252</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59566,7 +59566,7 @@
         <v>45748</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>46255</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59712,7 +59712,7 @@
         <v>46255</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59785,7 +59785,7 @@
         <v>44859</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59858,7 +59858,7 @@
         <v>46255</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59931,7 +59931,7 @@
         <v>45316</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>45390</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>44640</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         <v>46255</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45876</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>46255</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>45278</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45147</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60535,7 +60535,7 @@
         <v>46038</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60608,7 +60608,7 @@
         <v>45534</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60686,7 +60686,7 @@
         <v>46258</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>46255</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46255</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>46255</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>46255</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45362</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>45526</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61207,7 +61207,7 @@
         <v>45232</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61280,7 +61280,7 @@
         <v>45377</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61358,7 +61358,7 @@
         <v>46048</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61431,7 +61431,7 @@
         <v>44972</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61509,7 +61509,7 @@
         <v>45516</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61587,7 +61587,7 @@
         <v>45660</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61660,7 +61660,7 @@
         <v>45660</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61733,7 +61733,7 @@
         <v>45048</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61806,7 +61806,7 @@
         <v>46213</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>44686</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61957,7 +61957,7 @@
         <v>44747</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62035,7 +62035,7 @@
         <v>46217</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>46213</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>45516</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62259,7 +62259,7 @@
         <v>45516</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62337,7 +62337,7 @@
         <v>46262</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62415,7 +62415,7 @@
         <v>45762</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>44963</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62566,7 +62566,7 @@
         <v>45099</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45953</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62717,7 +62717,7 @@
         <v>45154</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62790,7 +62790,7 @@
         <v>45158</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62863,7 +62863,7 @@
         <v>45649</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         <v>44693</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45979</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63082,7 +63082,7 @@
         <v>44909</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63155,7 +63155,7 @@
         <v>45378</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63228,7 +63228,7 @@
         <v>46267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63306,7 +63306,7 @@
         <v>45442</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63384,7 +63384,7 @@
         <v>46265</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63457,7 +63457,7 @@
         <v>46265</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>45777</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63608,7 +63608,7 @@
         <v>44949</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63681,7 +63681,7 @@
         <v>45779</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63759,7 +63759,7 @@
         <v>46272</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63832,7 +63832,7 @@
         <v>46273</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>46273</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63983,7 +63983,7 @@
         <v>46076</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64056,7 +64056,7 @@
         <v>45216</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64129,7 +64129,7 @@
         <v>46104</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64207,7 +64207,7 @@
         <v>46104</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64285,7 +64285,7 @@
         <v>46275</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64363,7 +64363,7 @@
         <v>45734</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64436,7 +64436,7 @@
         <v>45140</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64509,7 +64509,7 @@
         <v>45995</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64582,7 +64582,7 @@
         <v>46276</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64655,7 +64655,7 @@
         <v>46276</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64728,7 +64728,7 @@
         <v>46276</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45786</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64874,7 +64874,7 @@
         <v>45786</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>45586</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65025,7 +65025,7 @@
         <v>46281</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         <v>45791</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65176,7 +65176,7 @@
         <v>45989</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65254,7 +65254,7 @@
         <v>45989</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65332,7 +65332,7 @@
         <v>45989</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         <v>45989</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65483,7 +65483,7 @@
         <v>45989</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65561,7 +65561,7 @@
         <v>45433</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65634,7 +65634,7 @@
         <v>46085</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65707,7 +65707,7 @@
         <v>45989</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65785,7 +65785,7 @@
         <v>46097</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65858,7 +65858,7 @@
         <v>46163</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65931,7 +65931,7 @@
         <v>45793</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66009,7 +66009,7 @@
         <v>45548</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66087,7 +66087,7 @@
         <v>46162</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66160,7 +66160,7 @@
         <v>45792</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66238,7 +66238,7 @@
         <v>46282</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66316,7 +66316,7 @@
         <v>46282</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66394,7 +66394,7 @@
         <v>45518</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66472,7 +66472,7 @@
         <v>45147</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66550,7 +66550,7 @@
         <v>45799</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         <v>46240</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66706,7 +66706,7 @@
         <v>46240</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66784,7 +66784,7 @@
         <v>45586</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66862,7 +66862,7 @@
         <v>46283</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66935,7 +66935,7 @@
         <v>45149</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67013,7 +67013,7 @@
         <v>45415</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67091,7 +67091,7 @@
         <v>45803</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67169,7 +67169,7 @@
         <v>44847</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67242,7 +67242,7 @@
         <v>45800</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67320,7 +67320,7 @@
         <v>45800</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67398,7 +67398,7 @@
         <v>45096</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67471,7 +67471,7 @@
         <v>45636</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67549,7 +67549,7 @@
         <v>45804</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67627,7 +67627,7 @@
         <v>45440</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67700,7 +67700,7 @@
         <v>45805</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67778,7 +67778,7 @@
         <v>45810</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67856,7 +67856,7 @@
         <v>45810</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67934,7 +67934,7 @@
         <v>44978</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68007,7 +68007,7 @@
         <v>45813</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68085,7 +68085,7 @@
         <v>45817</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         <v>45817</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68241,7 +68241,7 @@
         <v>44686</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68319,7 +68319,7 @@
         <v>45820</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68397,7 +68397,7 @@
         <v>45824</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68475,7 +68475,7 @@
         <v>45823</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68548,7 +68548,7 @@
         <v>45824</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68626,7 +68626,7 @@
         <v>45824</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68704,7 +68704,7 @@
         <v>45831</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68782,7 +68782,7 @@
         <v>45833</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68855,7 +68855,7 @@
         <v>45834</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68933,7 +68933,7 @@
         <v>45834</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69011,7 +69011,7 @@
         <v>45791</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69089,7 +69089,7 @@
         <v>45841</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69167,7 +69167,7 @@
         <v>45841</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69245,7 +69245,7 @@
         <v>45840</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69318,7 +69318,7 @@
         <v>45847</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69396,7 +69396,7 @@
         <v>45853</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>45853</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69552,7 +69552,7 @@
         <v>45205</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69630,7 +69630,7 @@
         <v>45862</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69703,7 +69703,7 @@
         <v>45874</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69781,7 +69781,7 @@
         <v>45874</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69859,7 +69859,7 @@
         <v>45874</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69937,7 +69937,7 @@
         <v>45877</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70015,7 +70015,7 @@
         <v>45877</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70093,7 +70093,7 @@
         <v>45443</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70171,7 +70171,7 @@
         <v>45883</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         <v>45883</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70327,7 +70327,7 @@
         <v>45883</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70400,7 +70400,7 @@
         <v>45883</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70473,7 +70473,7 @@
         <v>45883</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70551,7 +70551,7 @@
         <v>44574</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70624,7 +70624,7 @@
         <v>44491</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70697,7 +70697,7 @@
         <v>44566</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70770,7 +70770,7 @@
         <v>45061</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70843,7 +70843,7 @@
         <v>45393</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70916,7 +70916,7 @@
         <v>45061</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70989,7 +70989,7 @@
         <v>45393</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71062,7 +71062,7 @@
         <v>45061</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71135,7 +71135,7 @@
         <v>45393</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71208,7 +71208,7 @@
         <v>45748</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71286,7 +71286,7 @@
         <v>45932</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44753</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>44972</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45558</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45636</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>44972</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44838</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44494</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44881</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>45625</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44522</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45716</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45399</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44474</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46258</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45770</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45149</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45399</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>46073</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45903</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46270</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45399</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45349</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44657</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>46058</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45463</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45238</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>46255</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45625</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45490</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44888</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45478</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45205</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44698</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44648</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45665</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45799</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44664</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44972</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45546</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45709</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46286</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>45113</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45618</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45546</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45961</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>46255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44515</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44529</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45936</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45478</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>46093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45730</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45399</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45487</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45883</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45560</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45618</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45461</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45625</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44985</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>46148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45545</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45834</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>46252</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>46048</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46276</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45119</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45492</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46093</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44518</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>44532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45399</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45622</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45515</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45540</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45573</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45586</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45821</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45526</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44560</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45541</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>46163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46181</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45874</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45206</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46210</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45526</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45105</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44852</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45205</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44619</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44533</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44532</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44754</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44619</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44755</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44708</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44532</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>44805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44879</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44495</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44743</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45735</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45471</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45715</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44826</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45195</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45509</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45775</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45166</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44881</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45757</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>45399</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45419</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44802</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44847</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45450</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45236</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45232</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44855</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45377</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45443</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45453</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44847</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44847</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45436</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44859</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45516</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45463</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45883</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45883</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44972</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45526</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>44881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45478</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44852</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45147</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45793</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45518</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45238</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45149</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45232</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45884</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45884</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45552</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44972</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45483</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45534</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45890</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45890</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45890</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45890</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45415</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44515</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44515</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44972</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45636</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45800</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44890</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45541</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46045</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45316</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45560</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45207</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45216</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45403</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46055</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45518</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45558</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45915</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46049</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45636</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45625</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45408</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45803</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45659</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45659</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44568</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45805</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>45096</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45331</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45636</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44693</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45440</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44978</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45810</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45810</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45526</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45343</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45937</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46093</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45944</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45777</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45636</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45636</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45625</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45944</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45590</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45951</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45951</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45541</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45573</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45280</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>46111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46113</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>46113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45954</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45954</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>46113</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45730</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45254</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45558</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45957</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45931</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45957</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45957</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45957</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>44923</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45597</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45508</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46122</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45478</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45636</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45618</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45817</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>44628</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45238</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45635</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>44972</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>46129</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>46132</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45625</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45982</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45636</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45985</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45587</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45158</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>44743</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46129</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45693</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45388</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45993</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45996</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>45457</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45149</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45999</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45847</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45622</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45692</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>44686</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>46001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44640</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45505</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46006</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45478</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45820</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45748</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45453</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45993</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45656</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>44522</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45660</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45660</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>45297</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45709</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45823</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44957</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45992</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45238</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45238</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45730</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45730</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45232</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44909</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>44903</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45769</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45659</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>44628</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45831</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45754</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>46144</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>44923</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>44564</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>46150</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>46149</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45152</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45239</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45546</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45481</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45226</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45834</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45833</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>46153</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45791</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45894</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>44623</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45216</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45338</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>46160</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45653</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45048</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>44545</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45993</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45117</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>44545</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>46163</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45239</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45240</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45000</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>46163</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45756</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46168</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45847</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>44901</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45660</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45757</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>44847</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>46168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>46168</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45853</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45853</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>45205</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>46171</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>44914</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45862</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>44637</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45575</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>44942</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>46174</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>44532</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>46175</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>44505</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>46087</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44488</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>46174</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45297</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45571</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45571</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45152</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45492</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45492</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>44543</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45148</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>44522</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>44977</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>44977</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>44963</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45524</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45161</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>46181</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45636</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45656</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46183</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>45399</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46183</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>46183</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>46183</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45874</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45114</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45748</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45579</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45555</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46191</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45874</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>44515</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45874</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52741,7 +52741,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>45516</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>46184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45232</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45582</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45877</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45877</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45912</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>46196</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46196</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45376</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45159</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45972</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45972</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>46198</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45443</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45485</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>46199</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>45709</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>46198</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45048</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45349</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>46205</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>46204</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>46204</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>46205</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45883</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45883</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46204</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45883</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>46205</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>46204</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>46205</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>46209</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55615,7 +55615,7 @@
         <v>46209</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45589</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45583</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>46206</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46178</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>46252</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56078,7 +56078,7 @@
         <v>46252</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46252</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45800</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>45587</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>46252</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>46209</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>45617</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>46252</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46206</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46076</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45190</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45222</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>45762</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>46210</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45435</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45216</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45429</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45876</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>46210</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>46255</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>46255</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>46255</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>46255</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>46255</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45222</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>44615</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>46255</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>46255</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>46255</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>46258</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45148</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45225</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58874,7 +58874,7 @@
         <v>45237</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>46217</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59025,7 +59025,7 @@
         <v>46038</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>46213</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45254</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>44686</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59322,7 +59322,7 @@
         <v>46262</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46213</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>44747</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59551,7 +59551,7 @@
         <v>45092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45278</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45206</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45408</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45469</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59931,7 +59931,7 @@
         <v>45202</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>45953</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60082,7 +60082,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         <v>45756</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45756</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45979</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46267</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46265</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>44971</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46265</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>45435</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>45512</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45089</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>46273</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         <v>46273</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>46104</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>46104</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>44826</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61290,7 +61290,7 @@
         <v>46275</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>46276</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45531</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>46276</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>44657</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61665,7 +61665,7 @@
         <v>45574</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>45995</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>45090</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>45586</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44540</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45734</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>46282</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45989</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62430,7 +62430,7 @@
         <v>45989</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62508,7 +62508,7 @@
         <v>45989</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45989</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45989</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62737,7 +62737,7 @@
         <v>45989</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62815,7 +62815,7 @@
         <v>45730</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>45730</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45308</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45415</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45524</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>46085</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46097</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46162</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63414,7 +63414,7 @@
         <v>46281</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>46163</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63560,7 +63560,7 @@
         <v>45597</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63638,7 +63638,7 @@
         <v>45574</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63711,7 +63711,7 @@
         <v>45390</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>46240</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63867,7 +63867,7 @@
         <v>46240</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63945,7 +63945,7 @@
         <v>45586</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>45786</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64096,7 +64096,7 @@
         <v>45786</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64169,7 +64169,7 @@
         <v>44470</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>46283</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>46276</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>45495</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>44627</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64544,7 +64544,7 @@
         <v>44748</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45813</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>45996</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>45378</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>45442</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64924,7 +64924,7 @@
         <v>45526</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>46272</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>44995</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>46244</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>44857</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>46286</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>46076</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>46289</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>46157</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65606,7 +65606,7 @@
         <v>46048</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65679,7 +65679,7 @@
         <v>45140</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>45622</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65830,7 +65830,7 @@
         <v>46289</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65903,7 +65903,7 @@
         <v>46289</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>46289</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45730</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66127,7 +66127,7 @@
         <v>45225</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66205,7 +66205,7 @@
         <v>44657</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66278,7 +66278,7 @@
         <v>45000</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66429,7 +66429,7 @@
         <v>45428</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66507,7 +66507,7 @@
         <v>45042</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66585,7 +66585,7 @@
         <v>44488</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66658,7 +66658,7 @@
         <v>45520</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66736,7 +66736,7 @@
         <v>45478</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>44943</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66887,7 +66887,7 @@
         <v>45470</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66965,7 +66965,7 @@
         <v>45089</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>45154</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67111,7 +67111,7 @@
         <v>45000</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67184,7 +67184,7 @@
         <v>44963</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67257,7 +67257,7 @@
         <v>44515</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67330,7 +67330,7 @@
         <v>45469</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>44972</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>44972</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>44972</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67642,7 +67642,7 @@
         <v>45154</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67720,7 +67720,7 @@
         <v>45239</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67793,7 +67793,7 @@
         <v>45188</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67866,7 +67866,7 @@
         <v>45526</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67944,7 +67944,7 @@
         <v>45526</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68022,7 +68022,7 @@
         <v>45125</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>45649</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68168,7 +68168,7 @@
         <v>45236</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45475</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68324,7 +68324,7 @@
         <v>45195</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68402,7 +68402,7 @@
         <v>45442</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45743</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45229</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68626,7 +68626,7 @@
         <v>44977</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68699,7 +68699,7 @@
         <v>44658</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68772,7 +68772,7 @@
         <v>45147</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45730</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45730</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>45259</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69079,7 +69079,7 @@
         <v>45362</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69152,7 +69152,7 @@
         <v>45642</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69230,7 +69230,7 @@
         <v>44972</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69308,7 +69308,7 @@
         <v>45769</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69386,7 +69386,7 @@
         <v>44889</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69459,7 +69459,7 @@
         <v>45756</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69532,7 +69532,7 @@
         <v>45142</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69610,7 +69610,7 @@
         <v>45672</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69683,7 +69683,7 @@
         <v>45762</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69761,7 +69761,7 @@
         <v>45565</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69839,7 +69839,7 @@
         <v>45643</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69917,7 +69917,7 @@
         <v>45225</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69995,7 +69995,7 @@
         <v>45777</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70073,7 +70073,7 @@
         <v>44949</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70146,7 +70146,7 @@
         <v>45779</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>45216</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45140</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>45548</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70448,7 +70448,7 @@
         <v>45792</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         <v>45791</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70604,7 +70604,7 @@
         <v>45433</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70677,7 +70677,7 @@
         <v>44574</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>44566</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>44491</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45061</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>45393</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45061</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>45393</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71188,7 +71188,7 @@
         <v>45061</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71261,7 +71261,7 @@
         <v>45393</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71334,7 +71334,7 @@
         <v>45748</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45932</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44753</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>44972</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>45989</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>46104</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>44494</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>45558</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45989</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>45636</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>44972</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>44644</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>44838</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>44494</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>46076</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44881</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>45625</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>44972</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45989</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46142</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44972</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44522</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45716</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>45478</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>45399</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>45113</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44474</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>46258</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45887</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45770</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45149</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45915</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         <v>45051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45399</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>46073</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>45636</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45903</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>46270</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45399</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45636</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45349</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>46275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44657</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>46058</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45463</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45238</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44732</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45644</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>46255</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>45497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         <v>45625</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>45490</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44888</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45478</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45205</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44698</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44648</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>44515</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>45665</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>45799</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>45575</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>45629</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45589</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11686,7 +11686,7 @@
         <v>44664</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>44972</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>45546</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12497,7 +12497,7 @@
         <v>45545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45709</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45989</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>46009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46286</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
         <v>45113</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45618</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45546</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45961</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44806</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45461</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>46255</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44515</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>44529</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45936</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45478</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>45558</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>46093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>45730</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45399</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15669,7 +15669,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45487</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>46085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45883</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45560</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>45636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>45618</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45461</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>45625</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44518</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45817</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>45643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>44985</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>46148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45545</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45834</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>46252</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>46268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>46162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>46048</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46276</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45119</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45492</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>46093</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44518</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>44532</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45399</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45254</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>45622</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>45515</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45736</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45540</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>45573</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>45586</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>45821</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45526</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44560</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45541</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>46072</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
         <v>46163</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>46181</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45874</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45206</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46210</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>45526</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>46259</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45105</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44852</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22511,7 +22511,7 @@
         <v>46282</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44494</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45205</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23379,7 +23379,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23599,7 +23599,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>44810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>44619</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>44533</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24505,7 +24505,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>44532</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>44754</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>44619</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>44755</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>44532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25650,7 +25650,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>44852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44708</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44532</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>44805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>44879</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44495</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44743</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45735</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45471</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45715</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44826</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45195</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27029,7 +27029,7 @@
         <v>45509</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>45775</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45166</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>44881</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45757</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>45399</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>45419</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44802</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44847</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>45450</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27774,7 +27774,7 @@
         <v>45236</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45232</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>44855</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45377</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45443</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45453</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45453</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44847</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44847</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45436</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44859</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45516</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45463</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>45883</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45883</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>44972</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45526</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>44881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45278</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45478</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>44852</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29387,7 +29387,7 @@
         <v>45147</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45793</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29543,7 +29543,7 @@
         <v>45518</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45884</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>45238</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45149</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45232</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45884</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45884</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45552</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>44972</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30464,7 +30464,7 @@
         <v>45483</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45534</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>45890</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30698,7 +30698,7 @@
         <v>45890</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>45511</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45246</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45890</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45890</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>45415</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31166,7 +31166,7 @@
         <v>46038</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31244,7 +31244,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>44515</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>44515</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31468,7 +31468,7 @@
         <v>44972</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45636</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31624,7 +31624,7 @@
         <v>45800</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45800</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44890</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45541</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>46045</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32233,7 +32233,7 @@
         <v>45545</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>45316</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>45560</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45799</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45205</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45206</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45207</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>45216</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32857,7 +32857,7 @@
         <v>46055</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45403</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>46055</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33222,7 +33222,7 @@
         <v>44903</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33295,7 +33295,7 @@
         <v>45518</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45518</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45558</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45915</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>44917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46049</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>45636</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33821,7 +33821,7 @@
         <v>45915</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33894,7 +33894,7 @@
         <v>45625</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45408</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>45803</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>46066</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45659</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45659</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44568</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>45805</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>45096</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45331</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45636</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>44693</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45440</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44978</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45810</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45810</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45526</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45343</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35472,7 +35472,7 @@
         <v>44943</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35545,7 +35545,7 @@
         <v>44735</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35623,7 +35623,7 @@
         <v>45937</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>44981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>46093</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>45238</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>45944</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45777</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>45636</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45636</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45625</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45944</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36549,7 +36549,7 @@
         <v>45237</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36627,7 +36627,7 @@
         <v>46105</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36705,7 +36705,7 @@
         <v>45590</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>45951</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45463</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45951</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>45951</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44994</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45541</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45541</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45573</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>45280</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37455,7 +37455,7 @@
         <v>46111</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37533,7 +37533,7 @@
         <v>46111</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>45084</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46113</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>46113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37923,7 +37923,7 @@
         <v>45954</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38001,7 +38001,7 @@
         <v>45954</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38079,7 +38079,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>46113</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45730</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45254</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>45558</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38610,7 +38610,7 @@
         <v>45957</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38683,7 +38683,7 @@
         <v>45957</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>46121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45931</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45957</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45957</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>45957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39199,7 +39199,7 @@
         <v>45957</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45957</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45957</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>44923</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45597</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45508</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>46122</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>46122</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>46122</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39944,7 +39944,7 @@
         <v>45478</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>45636</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45618</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45817</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40334,7 +40334,7 @@
         <v>44628</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45238</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45635</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>44972</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>46129</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>46132</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45625</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40870,7 +40870,7 @@
         <v>46132</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40948,7 +40948,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         <v>45979</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45982</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41250,7 +41250,7 @@
         <v>45636</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45985</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>45985</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45587</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>45158</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>44743</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41708,7 +41708,7 @@
         <v>46129</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>45693</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>45388</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>45993</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>45996</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>45457</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>45149</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45999</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45847</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45622</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>45817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45692</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>44686</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>46001</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44640</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45251</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42916,7 +42916,7 @@
         <v>45505</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>46006</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45478</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45820</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45748</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45453</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45170</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43447,7 +43447,7 @@
         <v>45993</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43520,7 +43520,7 @@
         <v>45656</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>44522</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43676,7 +43676,7 @@
         <v>45660</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45660</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43822,7 +43822,7 @@
         <v>45297</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45709</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45823</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>44957</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44114,7 +44114,7 @@
         <v>45992</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45238</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>45238</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45238</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44499,7 +44499,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44650,7 +44650,7 @@
         <v>45730</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45730</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44806,7 +44806,7 @@
         <v>45232</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>44909</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>44903</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45025,7 +45025,7 @@
         <v>45769</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45103,7 +45103,7 @@
         <v>45659</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>44628</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>45831</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>45754</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>46144</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45483,7 +45483,7 @@
         <v>44923</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45556,7 +45556,7 @@
         <v>44564</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45629,7 +45629,7 @@
         <v>46150</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>46149</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45152</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>45239</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45546</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45481</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45226</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45190</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45834</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45833</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>46153</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46457,7 +46457,7 @@
         <v>45791</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46535,7 +46535,7 @@
         <v>45894</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46608,7 +46608,7 @@
         <v>44623</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45216</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45338</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>46157</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46915,7 +46915,7 @@
         <v>46160</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46988,7 +46988,7 @@
         <v>45653</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>45840</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45048</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>44545</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>46162</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>46048</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47509,7 +47509,7 @@
         <v>45993</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45117</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47660,7 +47660,7 @@
         <v>44545</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47733,7 +47733,7 @@
         <v>46163</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45239</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45240</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         <v>45000</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>46163</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45756</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>46168</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48342,7 +48342,7 @@
         <v>45847</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48420,7 +48420,7 @@
         <v>44901</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45660</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48566,7 +48566,7 @@
         <v>45757</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48644,7 +48644,7 @@
         <v>44847</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48717,7 +48717,7 @@
         <v>46168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>46168</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45853</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45853</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>45205</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49107,7 +49107,7 @@
         <v>46171</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49180,7 +49180,7 @@
         <v>44914</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>45862</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>44637</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45575</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>44942</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49555,7 +49555,7 @@
         <v>46174</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49628,7 +49628,7 @@
         <v>44532</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49701,7 +49701,7 @@
         <v>46175</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49779,7 +49779,7 @@
         <v>44505</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49852,7 +49852,7 @@
         <v>46087</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44488</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>46174</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>45297</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45571</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>45571</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50300,7 +50300,7 @@
         <v>45152</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50373,7 +50373,7 @@
         <v>45492</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>45492</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50529,7 +50529,7 @@
         <v>44543</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50602,7 +50602,7 @@
         <v>45148</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50680,7 +50680,7 @@
         <v>44522</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50758,7 +50758,7 @@
         <v>44977</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>44977</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50914,7 +50914,7 @@
         <v>44963</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45524</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45161</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>46181</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45636</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>45656</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46183</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>45399</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46183</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>46183</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>46183</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51835,7 +51835,7 @@
         <v>45874</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45114</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         <v>45748</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45579</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45555</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>46191</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>46191</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52434,7 +52434,7 @@
         <v>45874</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>44515</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>45874</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52741,7 +52741,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>45516</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>46184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>45232</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45582</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>45877</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45877</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45912</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>46196</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>46196</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53511,7 +53511,7 @@
         <v>45376</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45159</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>46199</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45972</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53803,7 +53803,7 @@
         <v>45972</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53876,7 +53876,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53954,7 +53954,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>46198</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>45443</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45485</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>46199</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>45709</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>46198</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54485,7 +54485,7 @@
         <v>45048</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45349</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>46205</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54704,7 +54704,7 @@
         <v>46204</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>46204</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54860,7 +54860,7 @@
         <v>46205</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54933,7 +54933,7 @@
         <v>45883</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45883</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55084,7 +55084,7 @@
         <v>46204</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55162,7 +55162,7 @@
         <v>46204</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55240,7 +55240,7 @@
         <v>45883</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>46205</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55386,7 +55386,7 @@
         <v>46204</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55464,7 +55464,7 @@
         <v>46205</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>46209</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55615,7 +55615,7 @@
         <v>46209</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55693,7 +55693,7 @@
         <v>45589</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55771,7 +55771,7 @@
         <v>45583</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55849,7 +55849,7 @@
         <v>46206</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55927,7 +55927,7 @@
         <v>46178</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56005,7 +56005,7 @@
         <v>46252</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56078,7 +56078,7 @@
         <v>46252</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>46252</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         <v>45800</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56302,7 +56302,7 @@
         <v>45587</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56380,7 +56380,7 @@
         <v>46252</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>46209</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56536,7 +56536,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56614,7 +56614,7 @@
         <v>45617</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56692,7 +56692,7 @@
         <v>46252</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>46206</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56843,7 +56843,7 @@
         <v>46076</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56916,7 +56916,7 @@
         <v>46252</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>46252</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>45190</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57223,7 +57223,7 @@
         <v>45222</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>45762</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57379,7 +57379,7 @@
         <v>46210</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>45435</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57530,7 +57530,7 @@
         <v>45216</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>45429</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45876</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>46210</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>46255</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>46255</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>46255</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>46255</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>46255</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>46255</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58270,7 +58270,7 @@
         <v>45222</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>44615</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>46255</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>46255</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58567,7 +58567,7 @@
         <v>46255</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58640,7 +58640,7 @@
         <v>46258</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58718,7 +58718,7 @@
         <v>45148</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45225</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58874,7 +58874,7 @@
         <v>45237</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>46217</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59025,7 +59025,7 @@
         <v>46038</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>46213</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>45254</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>44686</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59322,7 +59322,7 @@
         <v>46262</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46213</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>44747</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59551,7 +59551,7 @@
         <v>45092</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59629,7 +59629,7 @@
         <v>45278</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59702,7 +59702,7 @@
         <v>45206</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45408</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45469</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59931,7 +59931,7 @@
         <v>45202</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60009,7 +60009,7 @@
         <v>45953</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60082,7 +60082,7 @@
         <v>45756</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60160,7 +60160,7 @@
         <v>45756</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60233,7 +60233,7 @@
         <v>45756</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45979</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46267</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46265</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>44971</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46265</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>45435</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60754,7 +60754,7 @@
         <v>45512</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60832,7 +60832,7 @@
         <v>45089</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>46273</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         <v>46273</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>46104</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61134,7 +61134,7 @@
         <v>46104</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61212,7 +61212,7 @@
         <v>44826</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61290,7 +61290,7 @@
         <v>46275</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>46276</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45531</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>46276</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>44657</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61665,7 +61665,7 @@
         <v>45574</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>44522</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>45995</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>45090</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61972,7 +61972,7 @@
         <v>45586</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44540</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45734</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>46282</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62274,7 +62274,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45989</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62430,7 +62430,7 @@
         <v>45989</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62508,7 +62508,7 @@
         <v>45989</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62586,7 +62586,7 @@
         <v>45989</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45989</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62737,7 +62737,7 @@
         <v>45989</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62815,7 +62815,7 @@
         <v>45730</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62893,7 +62893,7 @@
         <v>45730</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62971,7 +62971,7 @@
         <v>45308</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45415</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63117,7 +63117,7 @@
         <v>45524</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63195,7 +63195,7 @@
         <v>46085</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63268,7 +63268,7 @@
         <v>46097</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63341,7 +63341,7 @@
         <v>46162</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63414,7 +63414,7 @@
         <v>46281</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>46163</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63560,7 +63560,7 @@
         <v>45597</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63638,7 +63638,7 @@
         <v>45574</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63711,7 +63711,7 @@
         <v>45390</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63789,7 +63789,7 @@
         <v>46240</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63867,7 +63867,7 @@
         <v>46240</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63945,7 +63945,7 @@
         <v>45586</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64023,7 +64023,7 @@
         <v>45786</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64096,7 +64096,7 @@
         <v>45786</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64169,7 +64169,7 @@
         <v>44470</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64247,7 +64247,7 @@
         <v>46283</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64320,7 +64320,7 @@
         <v>46276</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>45495</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64471,7 +64471,7 @@
         <v>44627</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64544,7 +64544,7 @@
         <v>44748</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64622,7 +64622,7 @@
         <v>45813</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64700,7 +64700,7 @@
         <v>45996</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64773,7 +64773,7 @@
         <v>45378</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>45442</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64924,7 +64924,7 @@
         <v>45526</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65002,7 +65002,7 @@
         <v>46272</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>44995</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>46244</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65231,7 +65231,7 @@
         <v>44857</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65304,7 +65304,7 @@
         <v>46286</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65382,7 +65382,7 @@
         <v>46076</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         <v>46289</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65528,7 +65528,7 @@
         <v>46157</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65606,7 +65606,7 @@
         <v>46048</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65679,7 +65679,7 @@
         <v>45140</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         <v>45622</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65830,7 +65830,7 @@
         <v>46289</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65903,7 +65903,7 @@
         <v>46289</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65976,7 +65976,7 @@
         <v>46289</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66049,7 +66049,7 @@
         <v>45730</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66127,7 +66127,7 @@
         <v>45225</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66205,7 +66205,7 @@
         <v>44657</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66278,7 +66278,7 @@
         <v>45000</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66351,7 +66351,7 @@
         <v>46248</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66429,7 +66429,7 @@
         <v>45428</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66507,7 +66507,7 @@
         <v>45042</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66585,7 +66585,7 @@
         <v>44488</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66658,7 +66658,7 @@
         <v>45520</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66736,7 +66736,7 @@
         <v>45478</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66814,7 +66814,7 @@
         <v>44943</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66887,7 +66887,7 @@
         <v>45470</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66965,7 +66965,7 @@
         <v>45089</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67038,7 +67038,7 @@
         <v>45154</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67111,7 +67111,7 @@
         <v>45000</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67184,7 +67184,7 @@
         <v>44963</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67257,7 +67257,7 @@
         <v>44515</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67330,7 +67330,7 @@
         <v>45469</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67408,7 +67408,7 @@
         <v>44972</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67486,7 +67486,7 @@
         <v>44972</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67564,7 +67564,7 @@
         <v>44972</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67642,7 +67642,7 @@
         <v>45154</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67720,7 +67720,7 @@
         <v>45239</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67793,7 +67793,7 @@
         <v>45188</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67866,7 +67866,7 @@
         <v>45526</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67944,7 +67944,7 @@
         <v>45526</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68022,7 +68022,7 @@
         <v>45125</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68095,7 +68095,7 @@
         <v>45649</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68168,7 +68168,7 @@
         <v>45236</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68246,7 +68246,7 @@
         <v>45475</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68324,7 +68324,7 @@
         <v>45195</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68402,7 +68402,7 @@
         <v>45442</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68480,7 +68480,7 @@
         <v>45743</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68553,7 +68553,7 @@
         <v>45229</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68626,7 +68626,7 @@
         <v>44977</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68699,7 +68699,7 @@
         <v>44658</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68772,7 +68772,7 @@
         <v>45147</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68850,7 +68850,7 @@
         <v>45730</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68928,7 +68928,7 @@
         <v>45730</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69006,7 +69006,7 @@
         <v>45259</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69079,7 +69079,7 @@
         <v>45362</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69152,7 +69152,7 @@
         <v>45642</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69230,7 +69230,7 @@
         <v>44972</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69308,7 +69308,7 @@
         <v>45769</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69386,7 +69386,7 @@
         <v>44889</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69459,7 +69459,7 @@
         <v>45756</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69532,7 +69532,7 @@
         <v>45142</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69610,7 +69610,7 @@
         <v>45672</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69683,7 +69683,7 @@
         <v>45762</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69761,7 +69761,7 @@
         <v>45565</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69839,7 +69839,7 @@
         <v>45643</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69917,7 +69917,7 @@
         <v>45225</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69995,7 +69995,7 @@
         <v>45777</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70073,7 +70073,7 @@
         <v>44949</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70146,7 +70146,7 @@
         <v>45779</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70224,7 +70224,7 @@
         <v>45216</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70297,7 +70297,7 @@
         <v>45140</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         <v>45548</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70448,7 +70448,7 @@
         <v>45792</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70526,7 +70526,7 @@
         <v>45791</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70604,7 +70604,7 @@
         <v>45433</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70677,7 +70677,7 @@
         <v>44574</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         <v>44566</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70823,7 +70823,7 @@
         <v>44491</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70896,7 +70896,7 @@
         <v>45061</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70969,7 +70969,7 @@
         <v>45393</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71042,7 +71042,7 @@
         <v>45061</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71115,7 +71115,7 @@
         <v>45393</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71188,7 +71188,7 @@
         <v>45061</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71261,7 +71261,7 @@
         <v>45393</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71334,7 +71334,7 @@
         <v>45748</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71412,7 +71412,7 @@
         <v>45932</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44972</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>44644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44494</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45625</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46141</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>44522</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45561</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45716</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45295</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45399</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45113</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45054</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44474</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46258</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45770</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45149</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45915</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>45636</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>46270</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44657</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45349</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45208</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46097</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45463</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45238</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44732</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46255</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45490</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45764</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44888</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45478</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45665</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45799</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45589</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44664</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44972</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44515</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45552</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>46286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44515</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45961</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45618</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45278</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45545</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45113</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46282</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46255</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46080</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45478</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45561</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45560</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45730</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45399</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44529</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45487</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>46003</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45643</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45560</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45636</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45461</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45625</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45834</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45545</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45618</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45883</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46273</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45751</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>46162</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46276</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46252</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45492</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>46093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44852</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>45526</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45515</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45206</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45540</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45874</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44560</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46163</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44494</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46181</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45523</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46210</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46259</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45573</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45399</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44533</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44619</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44532</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>44754</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44619</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44755</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44708</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44532</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>44879</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>44617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44495</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44743</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44972</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45597</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44914</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45471</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45560</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45470</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45643</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45481</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45140</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45660</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44657</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45518</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45254</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45541</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45884</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45190</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45000</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44889</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45622</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>44627</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45478</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45571</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45571</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46006</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45884</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45238</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45791</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44923</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45693</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45433</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44522</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45890</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45890</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45890</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45114</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45552</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44748</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45793</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45636</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45548</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46038</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45403</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45512</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45545</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45237</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>46045</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45518</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45555</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45558</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45636</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45147</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45531</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45149</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45415</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45803</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45800</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45800</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45096</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45636</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45804</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45440</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44802</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46055</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45573</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45331</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45625</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45730</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45730</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>46049</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44971</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45469</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45232</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45526</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45526</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45659</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45810</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45659</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45656</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44568</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45338</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45937</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45195</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45636</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45625</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45636</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45636</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45597</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45944</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44852</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45944</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>44978</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45951</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45954</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45954</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45308</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45259</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44515</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44515</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45579</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45672</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44826</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45558</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>44847</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>44522</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45508</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45957</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45957</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45957</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45957</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45463</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45957</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45730</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45730</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45240</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45817</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44505</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>46093</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>44686</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45636</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45777</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45636</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45730</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45730</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45656</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>46105</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45463</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45161</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45625</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45590</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45979</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45280</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45981</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45618</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45495</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45820</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46111</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>45985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46111</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>45982</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>45226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>46114</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>46113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>46113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45343</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46113</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45824</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45823</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45931</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45769</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46122</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46122</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45735</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>46122</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45993</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45216</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45483</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44543</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>46125</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45635</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46129</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45996</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44963</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45260</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45999</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>44855</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46132</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>46132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>46132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45833</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>46129</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>44540</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45251</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>45992</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45709</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45125</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45161</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45408</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45993</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45757</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45847</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45505</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44488</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>44972</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45853</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45775</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45546</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45642</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45089</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45399</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>44977</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45862</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45415</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>45388</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>44515</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45659</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45692</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45887,7 +45887,7 @@
         <v>45643</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45142</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45435</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45216</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44957</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44972</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>46144</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45161</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45715</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44658</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46149</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45636</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44847</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>44847</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>46153</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45762</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>46150</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45754</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45000</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44917</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45894</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45478</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44623</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>46157</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45225</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45653</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45874</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45993</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46048</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45874</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45874</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>46162</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44911</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>44545</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46163</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45877</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45195</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45877</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>44972</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45478</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46168</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>44994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>46168</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45757</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         <v>45443</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45232</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>44657</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45436</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46174</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45089</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45442</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45883</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>46171</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45883</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45216</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45883</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>45883</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45883</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>46087</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>46175</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45478</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45884</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45435</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45399</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45622</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46181</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>45232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46183</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45428</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>46183</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45574</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46183</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>46183</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45457</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52206,7 +52206,7 @@
         <v>45582</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52284,7 +52284,7 @@
         <v>45408</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45453</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52435,7 +52435,7 @@
         <v>45443</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         <v>44881</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>46191</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>46191</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45756</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45207</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45225</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>46196</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>46196</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45912</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>46198</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45972</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45972</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45148</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46198</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45236</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>46199</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45709</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54111,7 +54111,7 @@
         <v>44903</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         <v>45222</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54262,7 +54262,7 @@
         <v>45429</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45617</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>46204</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>46205</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>46204</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>46204</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>46204</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>44637</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>46204</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45475</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>46206</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>46076</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>46205</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>46205</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>46205</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>45800</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>46209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>46209</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>46210</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>46209</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45583</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>46210</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45526</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45246</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46178</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45589</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56484,7 +56484,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>46255</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45149</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>46255</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>45876</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>46255</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45152</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>46038</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>45511</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>46258</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>45526</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45509</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46213</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57541,7 +57541,7 @@
         <v>44686</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>44532</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>44995</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46217</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>46213</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45239</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>46262</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>44881</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>45953</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>45756</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45756</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58359,7 +58359,7 @@
         <v>45756</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58432,7 +58432,7 @@
         <v>45565</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>44972</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45979</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46267</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46273</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>45159</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45190</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45297</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>44972</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45117</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46104</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46104</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>46275</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45734</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>46276</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>46276</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>44628</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>45485</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45586</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>46281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45518</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>45989</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45989</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60181,7 +60181,7 @@
         <v>45989</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45989</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60337,7 +60337,7 @@
         <v>45092</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>46085</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45989</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45545</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60644,7 +60644,7 @@
         <v>46097</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45238</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>45238</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46163</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>45376</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>46282</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>45206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45225</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>44522</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>45084</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45154</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>45492</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45492</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45469</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         <v>46240</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>46240</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61955,7 +61955,7 @@
         <v>46283</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>45090</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62106,7 +62106,7 @@
         <v>45541</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62184,7 +62184,7 @@
         <v>45996</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>46276</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>46286</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>46244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45813</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62564,7 +62564,7 @@
         <v>45152</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62637,7 +62637,7 @@
         <v>45236</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>45450</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62793,7 +62793,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45278</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62939,7 +62939,7 @@
         <v>45786</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63012,7 +63012,7 @@
         <v>45786</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45756</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>45748</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>44743</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>46289</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>44972</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>44826</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>46289</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45000</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>44943</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>46289</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45300</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>44628</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>45042</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>46157</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45222</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>46048</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45995</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>44923</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64507,7 +64507,7 @@
         <v>46248</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>45419</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64658,7 +64658,7 @@
         <v>45524</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>44564</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>46076</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>46252</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>46252</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45587</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>44977</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>44977</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>46252</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>44857</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>45587</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>46252</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>45586</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45349</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>44615</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46252</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46252</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46265</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46255</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>46255</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>44735</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>44488</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>46255</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45453</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>45453</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>46255</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>45730</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>45730</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>45989</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66835,7 +66835,7 @@
         <v>45769</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>46162</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66986,7 +66986,7 @@
         <v>46265</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67059,7 +67059,7 @@
         <v>46255</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>46255</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>46252</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>45524</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45238</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>45575</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67517,7 +67517,7 @@
         <v>45520</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67595,7 +67595,7 @@
         <v>45254</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67673,7 +67673,7 @@
         <v>45743</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
         <v>44903</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>45748</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67892,7 +67892,7 @@
         <v>44859</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45316</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68043,7 +68043,7 @@
         <v>45390</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68121,7 +68121,7 @@
         <v>44640</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68194,7 +68194,7 @@
         <v>45278</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68272,7 +68272,7 @@
         <v>45147</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45534</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68428,7 +68428,7 @@
         <v>45362</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68501,7 +68501,7 @@
         <v>45526</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68579,7 +68579,7 @@
         <v>45232</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68652,7 +68652,7 @@
         <v>45377</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68730,7 +68730,7 @@
         <v>44972</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68808,7 +68808,7 @@
         <v>45516</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>45660</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45660</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>45048</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>44747</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>45516</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69261,7 +69261,7 @@
         <v>45516</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69339,7 +69339,7 @@
         <v>45762</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69417,7 +69417,7 @@
         <v>44963</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69490,7 +69490,7 @@
         <v>45099</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69568,7 +69568,7 @@
         <v>45154</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69641,7 +69641,7 @@
         <v>45158</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69714,7 +69714,7 @@
         <v>45649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69787,7 +69787,7 @@
         <v>44693</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69860,7 +69860,7 @@
         <v>44909</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69933,7 +69933,7 @@
         <v>45378</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70006,7 +70006,7 @@
         <v>45442</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70084,7 +70084,7 @@
         <v>45777</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70162,7 +70162,7 @@
         <v>44949</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>45779</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70313,7 +70313,7 @@
         <v>45216</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45140</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70459,7 +70459,7 @@
         <v>44574</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70532,7 +70532,7 @@
         <v>44491</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70605,7 +70605,7 @@
         <v>44566</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>45061</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>45393</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70824,7 +70824,7 @@
         <v>45061</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70897,7 +70897,7 @@
         <v>45393</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70970,7 +70970,7 @@
         <v>45061</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71043,7 +71043,7 @@
         <v>45393</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71116,7 +71116,7 @@
         <v>45748</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71194,7 +71194,7 @@
         <v>45932</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44972</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>44644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44494</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45625</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46141</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>44522</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45561</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45716</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45295</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>45478</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45399</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45113</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45054</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44474</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>46258</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>45509</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>44945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>45770</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45149</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6635,7 +6635,7 @@
         <v>45915</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45051</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>45636</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>46270</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>45636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44657</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45349</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45208</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>46097</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>46058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>45463</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45238</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>44964</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>44732</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>46255</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45490</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45205</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>45764</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>44888</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>45478</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45665</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45799</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>45575</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45629</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>45589</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45573</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>44664</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>44972</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11858,7 +11858,7 @@
         <v>44515</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45552</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>45188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12775,7 +12775,7 @@
         <v>46286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44515</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45461</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>45546</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45961</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44806</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>45618</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45278</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45545</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45113</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46282</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46255</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>46080</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14481,7 +14481,7 @@
         <v>45558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45478</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45561</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45560</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15044,7 +15044,7 @@
         <v>46062</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>46093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45730</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45399</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44529</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45487</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46085</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>46003</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45643</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45560</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>45636</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16611,7 +16611,7 @@
         <v>45119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45461</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45937</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45625</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45817</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45834</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45545</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45618</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>45883</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>46268</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>46273</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>45751</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>46162</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>44985</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46276</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46252</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45541</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
         <v>45492</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>46093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44852</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>45526</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44911</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45804</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>45105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>45254</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20260,7 +20260,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45515</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45206</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45821</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45540</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45874</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>44560</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>46163</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>44494</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46181</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45582</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45523</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>46210</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46259</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45573</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45205</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>46163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45589</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45399</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>44810</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>44859</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>44533</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>44619</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>44532</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>44817</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>44743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>44743</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>44889</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25052,7 +25052,7 @@
         <v>44754</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44619</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>44482</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>44755</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44532</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>44743</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>44852</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>44708</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>44532</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>44805</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>44879</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44799</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>44617</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>44545</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>44495</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26431,7 +26431,7 @@
         <v>44837</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44743</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44972</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>45597</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44914</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45471</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>45560</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45470</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45643</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27196,7 +27196,7 @@
         <v>45481</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45140</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>45660</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>45048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27493,7 +27493,7 @@
         <v>44657</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27566,7 +27566,7 @@
         <v>45518</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>45254</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
         <v>45541</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45541</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45884</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45190</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>46001</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45000</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>44889</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45237</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45622</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>44627</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>45478</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28550,7 +28550,7 @@
         <v>45571</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45571</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>46006</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45884</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>45238</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28920,7 +28920,7 @@
         <v>44901</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28993,7 +28993,7 @@
         <v>45791</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>44923</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>44942</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45693</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45433</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>44522</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29446,7 +29446,7 @@
         <v>44515</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29519,7 +29519,7 @@
         <v>45890</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>45890</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>45890</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>45114</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29982,7 +29982,7 @@
         <v>45552</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>44748</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45202</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45793</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45636</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45548</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>46038</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45403</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45512</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45545</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
         <v>45237</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>45792</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>46045</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45915</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31132,7 +31132,7 @@
         <v>45518</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45545</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31361,7 +31361,7 @@
         <v>45555</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31434,7 +31434,7 @@
         <v>45558</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45636</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45147</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45531</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>45799</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45149</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>45415</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>45803</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45800</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45800</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45096</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45636</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45804</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32511,7 +32511,7 @@
         <v>45239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32584,7 +32584,7 @@
         <v>45440</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32657,7 +32657,7 @@
         <v>45805</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>44802</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>46055</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>46055</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32959,7 +32959,7 @@
         <v>46055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>46055</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33105,7 +33105,7 @@
         <v>45573</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45331</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33251,7 +33251,7 @@
         <v>45625</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33329,7 +33329,7 @@
         <v>45730</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>45730</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>46049</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>44971</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>45469</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33709,7 +33709,7 @@
         <v>45232</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45526</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33860,7 +33860,7 @@
         <v>45526</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45659</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45810</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45659</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45659</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45656</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>46066</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34391,7 +34391,7 @@
         <v>44568</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34464,7 +34464,7 @@
         <v>45338</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46070</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>45937</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>45195</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45238</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45238</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45636</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45625</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>45636</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45636</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>45597</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35312,7 +35312,7 @@
         <v>45810</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35390,7 +35390,7 @@
         <v>45944</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44852</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45944</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35624,7 +35624,7 @@
         <v>44978</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>45239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45951</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45951</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45954</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45954</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45957</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>45308</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>45259</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36442,7 +36442,7 @@
         <v>44515</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>44515</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45579</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45672</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44826</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45558</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>44847</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>44522</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45508</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45957</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>45957</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45957</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>45957</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45957</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45957</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45463</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>45957</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45957</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37849,7 +37849,7 @@
         <v>45730</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>45730</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38005,7 +38005,7 @@
         <v>45957</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45240</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>45817</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45817</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38312,7 +38312,7 @@
         <v>44505</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38385,7 +38385,7 @@
         <v>46093</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38463,7 +38463,7 @@
         <v>44686</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45636</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>45777</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38770,7 +38770,7 @@
         <v>45636</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45730</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>45730</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45656</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>46105</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45463</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45161</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>45625</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39467,7 +39467,7 @@
         <v>45590</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>45979</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45280</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>45981</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45618</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>45495</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>45820</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46111</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40071,7 +40071,7 @@
         <v>45985</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>45985</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46111</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40300,7 +40300,7 @@
         <v>45982</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>45226</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40456,7 +40456,7 @@
         <v>46114</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>46113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40607,7 +40607,7 @@
         <v>46113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45343</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>46113</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45824</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40914,7 +40914,7 @@
         <v>45823</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40987,7 +40987,7 @@
         <v>45931</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45769</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44981</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41289,7 +41289,7 @@
         <v>45170</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>46122</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41440,7 +41440,7 @@
         <v>46122</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45735</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>46122</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45993</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>45216</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45483</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>44543</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42044,7 +42044,7 @@
         <v>46125</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45635</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42195,7 +42195,7 @@
         <v>46129</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42273,7 +42273,7 @@
         <v>45996</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>44963</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45260</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45831</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42575,7 +42575,7 @@
         <v>45999</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>44855</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>46132</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>46132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>46132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>45833</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45834</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>46129</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43189,7 +43189,7 @@
         <v>44540</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43262,7 +43262,7 @@
         <v>45251</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>45992</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43408,7 +43408,7 @@
         <v>45709</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45791</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43559,7 +43559,7 @@
         <v>45125</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45161</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>45408</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45993</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>45841</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>45757</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45206</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>45840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45847</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44231,7 +44231,7 @@
         <v>45505</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45847</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44382,7 +44382,7 @@
         <v>44488</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>44972</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>45853</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45853</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>45574</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45775</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45546</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45238</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45642</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45069,7 +45069,7 @@
         <v>45089</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
         <v>45399</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45215,7 +45215,7 @@
         <v>44977</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>45205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45862</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45439,7 +45439,7 @@
         <v>45415</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45229</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>45388</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45658,7 +45658,7 @@
         <v>44515</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45659</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45692</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45887,7 +45887,7 @@
         <v>45643</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45142</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46043,7 +46043,7 @@
         <v>45435</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46121,7 +46121,7 @@
         <v>45216</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44957</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46272,7 +46272,7 @@
         <v>44972</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>46144</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46423,7 +46423,7 @@
         <v>45161</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46501,7 +46501,7 @@
         <v>45715</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>44658</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46652,7 +46652,7 @@
         <v>46149</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45636</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>44847</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>44847</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46954,7 +46954,7 @@
         <v>46153</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>45762</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>46150</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45754</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45000</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44917</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45894</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47480,7 +47480,7 @@
         <v>45478</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44623</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>46157</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45225</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45653</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45874</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>46160</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>45993</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>46048</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48167,7 +48167,7 @@
         <v>44545</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48240,7 +48240,7 @@
         <v>45874</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48318,7 +48318,7 @@
         <v>45874</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48396,7 +48396,7 @@
         <v>46162</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48469,7 +48469,7 @@
         <v>44911</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>46163</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         <v>44545</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48698,7 +48698,7 @@
         <v>46163</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45877</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>45195</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45877</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49010,7 +49010,7 @@
         <v>44972</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49088,7 +49088,7 @@
         <v>45478</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>46168</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>44994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>46168</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46168</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>45757</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         <v>45443</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49634,7 +49634,7 @@
         <v>44943</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
         <v>45232</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>44657</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45297</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49926,7 +49926,7 @@
         <v>45436</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50004,7 +50004,7 @@
         <v>46174</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50077,7 +50077,7 @@
         <v>45089</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>45442</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50228,7 +50228,7 @@
         <v>46174</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45883</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50384,7 +50384,7 @@
         <v>46171</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50457,7 +50457,7 @@
         <v>45883</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50535,7 +50535,7 @@
         <v>45216</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50613,7 +50613,7 @@
         <v>45883</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>45883</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50759,7 +50759,7 @@
         <v>45883</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>46087</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>46175</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50993,7 +50993,7 @@
         <v>45478</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45884</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>45435</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>45399</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51300,7 +51300,7 @@
         <v>45622</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51378,7 +51378,7 @@
         <v>46181</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51456,7 +51456,7 @@
         <v>45232</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51602,7 +51602,7 @@
         <v>46183</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51675,7 +51675,7 @@
         <v>45428</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>46183</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45574</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46183</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>46183</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52055,7 +52055,7 @@
         <v>46189</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>45457</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52206,7 +52206,7 @@
         <v>45582</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52284,7 +52284,7 @@
         <v>45408</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45453</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52435,7 +52435,7 @@
         <v>45443</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52513,7 +52513,7 @@
         <v>44881</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52586,7 +52586,7 @@
         <v>46184</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52664,7 +52664,7 @@
         <v>46191</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52742,7 +52742,7 @@
         <v>46191</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45756</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>45207</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45225</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>46196</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>46196</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45912</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>46198</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45972</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45972</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45148</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45205</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53731,7 +53731,7 @@
         <v>46198</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53887,7 +53887,7 @@
         <v>45236</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>46199</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54038,7 +54038,7 @@
         <v>45709</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54111,7 +54111,7 @@
         <v>44903</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         <v>45222</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54262,7 +54262,7 @@
         <v>45429</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54340,7 +54340,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54418,7 +54418,7 @@
         <v>45617</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>46204</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54574,7 +54574,7 @@
         <v>46205</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54647,7 +54647,7 @@
         <v>46204</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>46204</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>46204</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>44637</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>46204</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55032,7 +55032,7 @@
         <v>45475</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>46206</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>46076</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>46206</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55339,7 +55339,7 @@
         <v>46205</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55412,7 +55412,7 @@
         <v>46205</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>46205</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>45800</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>46209</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>46209</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>46210</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55865,7 +55865,7 @@
         <v>46209</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>45583</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>46210</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45526</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56172,7 +56172,7 @@
         <v>45246</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56250,7 +56250,7 @@
         <v>46209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56328,7 +56328,7 @@
         <v>46178</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56406,7 +56406,7 @@
         <v>45589</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56484,7 +56484,7 @@
         <v>46209</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56562,7 +56562,7 @@
         <v>46255</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56635,7 +56635,7 @@
         <v>45149</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56713,7 +56713,7 @@
         <v>46255</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>45876</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56859,7 +56859,7 @@
         <v>46255</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45152</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57005,7 +57005,7 @@
         <v>45148</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>46038</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>45511</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57234,7 +57234,7 @@
         <v>46258</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57312,7 +57312,7 @@
         <v>45526</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57390,7 +57390,7 @@
         <v>45509</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57468,7 +57468,7 @@
         <v>46213</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57541,7 +57541,7 @@
         <v>44686</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57619,7 +57619,7 @@
         <v>44532</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57692,7 +57692,7 @@
         <v>44995</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46217</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57843,7 +57843,7 @@
         <v>46213</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57916,7 +57916,7 @@
         <v>45239</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>46262</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>44881</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>45953</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         <v>45756</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58286,7 +58286,7 @@
         <v>45756</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58359,7 +58359,7 @@
         <v>45756</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58432,7 +58432,7 @@
         <v>45565</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>44972</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45979</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58661,7 +58661,7 @@
         <v>46267</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58739,7 +58739,7 @@
         <v>46273</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58817,7 +58817,7 @@
         <v>45159</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45190</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45297</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>44972</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>45117</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>46104</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59275,7 +59275,7 @@
         <v>46104</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>46275</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59431,7 +59431,7 @@
         <v>45734</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59504,7 +59504,7 @@
         <v>46276</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>46276</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>44628</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>45485</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45586</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59874,7 +59874,7 @@
         <v>46281</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45518</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60025,7 +60025,7 @@
         <v>45989</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60103,7 +60103,7 @@
         <v>45989</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60181,7 +60181,7 @@
         <v>45989</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60259,7 +60259,7 @@
         <v>45989</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60337,7 +60337,7 @@
         <v>45092</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60415,7 +60415,7 @@
         <v>46085</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>45989</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60566,7 +60566,7 @@
         <v>45545</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60644,7 +60644,7 @@
         <v>46097</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60717,7 +60717,7 @@
         <v>45238</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60795,7 +60795,7 @@
         <v>45238</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>46163</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>45376</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>46282</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61097,7 +61097,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61175,7 +61175,7 @@
         <v>45206</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45225</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>44522</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>45084</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>45154</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61565,7 +61565,7 @@
         <v>45492</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61643,7 +61643,7 @@
         <v>45492</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61721,7 +61721,7 @@
         <v>45469</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61799,7 +61799,7 @@
         <v>46240</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>46240</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61955,7 +61955,7 @@
         <v>46283</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>45090</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62106,7 +62106,7 @@
         <v>45541</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62184,7 +62184,7 @@
         <v>45996</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>46276</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62330,7 +62330,7 @@
         <v>46286</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>46244</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>45813</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62564,7 +62564,7 @@
         <v>45152</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62637,7 +62637,7 @@
         <v>45236</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>45450</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62793,7 +62793,7 @@
         <v>46272</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62866,7 +62866,7 @@
         <v>45278</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62939,7 +62939,7 @@
         <v>45786</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63012,7 +63012,7 @@
         <v>45786</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63085,7 +63085,7 @@
         <v>45756</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63163,7 +63163,7 @@
         <v>45748</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63236,7 +63236,7 @@
         <v>44743</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63314,7 +63314,7 @@
         <v>46289</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63387,7 +63387,7 @@
         <v>44972</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63465,7 +63465,7 @@
         <v>44826</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>46289</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45000</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>44943</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>46289</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>46289</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>45300</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>44628</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64049,7 +64049,7 @@
         <v>45042</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>46157</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>45222</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>46048</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45995</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>44923</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64507,7 +64507,7 @@
         <v>46248</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64585,7 +64585,7 @@
         <v>45419</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64658,7 +64658,7 @@
         <v>45524</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64736,7 +64736,7 @@
         <v>44564</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>46076</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64882,7 +64882,7 @@
         <v>46252</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64955,7 +64955,7 @@
         <v>46252</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65033,7 +65033,7 @@
         <v>45587</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>44977</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65189,7 +65189,7 @@
         <v>44977</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65267,7 +65267,7 @@
         <v>46252</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65340,7 +65340,7 @@
         <v>44857</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65413,7 +65413,7 @@
         <v>45587</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65491,7 +65491,7 @@
         <v>46252</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>45586</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65642,7 +65642,7 @@
         <v>45349</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>44615</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46252</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46252</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46265</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46255</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>46255</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66153,7 +66153,7 @@
         <v>44735</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66231,7 +66231,7 @@
         <v>44488</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         <v>46255</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66377,7 +66377,7 @@
         <v>45453</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66455,7 +66455,7 @@
         <v>45453</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>46255</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>45730</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66684,7 +66684,7 @@
         <v>45730</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66762,7 +66762,7 @@
         <v>45989</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66835,7 +66835,7 @@
         <v>45769</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66913,7 +66913,7 @@
         <v>46162</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66986,7 +66986,7 @@
         <v>46265</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67059,7 +67059,7 @@
         <v>46255</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67132,7 +67132,7 @@
         <v>46255</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67205,7 +67205,7 @@
         <v>46252</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67283,7 +67283,7 @@
         <v>45524</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67361,7 +67361,7 @@
         <v>45238</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67439,7 +67439,7 @@
         <v>45575</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67517,7 +67517,7 @@
         <v>45520</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67595,7 +67595,7 @@
         <v>45254</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67673,7 +67673,7 @@
         <v>45743</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67746,7 +67746,7 @@
         <v>44903</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67819,7 +67819,7 @@
         <v>45748</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67892,7 +67892,7 @@
         <v>44859</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67965,7 +67965,7 @@
         <v>45316</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68043,7 +68043,7 @@
         <v>45390</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68121,7 +68121,7 @@
         <v>44640</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68194,7 +68194,7 @@
         <v>45278</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68272,7 +68272,7 @@
         <v>45147</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45534</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68428,7 +68428,7 @@
         <v>45362</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68501,7 +68501,7 @@
         <v>45526</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68579,7 +68579,7 @@
         <v>45232</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68652,7 +68652,7 @@
         <v>45377</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68730,7 +68730,7 @@
         <v>44972</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68808,7 +68808,7 @@
         <v>45516</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68886,7 +68886,7 @@
         <v>45660</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68959,7 +68959,7 @@
         <v>45660</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69032,7 +69032,7 @@
         <v>45048</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69105,7 +69105,7 @@
         <v>44747</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69183,7 +69183,7 @@
         <v>45516</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69261,7 +69261,7 @@
         <v>45516</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69339,7 +69339,7 @@
         <v>45762</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69417,7 +69417,7 @@
         <v>44963</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69490,7 +69490,7 @@
         <v>45099</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69568,7 +69568,7 @@
         <v>45154</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69641,7 +69641,7 @@
         <v>45158</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69714,7 +69714,7 @@
         <v>45649</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69787,7 +69787,7 @@
         <v>44693</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69860,7 +69860,7 @@
         <v>44909</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69933,7 +69933,7 @@
         <v>45378</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70006,7 +70006,7 @@
         <v>45442</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70084,7 +70084,7 @@
         <v>45777</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70162,7 +70162,7 @@
         <v>44949</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70235,7 +70235,7 @@
         <v>45779</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70313,7 +70313,7 @@
         <v>45216</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70386,7 +70386,7 @@
         <v>45140</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70459,7 +70459,7 @@
         <v>44574</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70532,7 +70532,7 @@
         <v>44491</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70605,7 +70605,7 @@
         <v>44566</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70678,7 +70678,7 @@
         <v>45061</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70751,7 +70751,7 @@
         <v>45393</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70824,7 +70824,7 @@
         <v>45061</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70897,7 +70897,7 @@
         <v>45393</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70970,7 +70970,7 @@
         <v>45061</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71043,7 +71043,7 @@
         <v>45393</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71116,7 +71116,7 @@
         <v>45748</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71194,7 +71194,7 @@
         <v>45932</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44972</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>44644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46141</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>44522</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45295</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45716</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45399</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45113</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46276</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>45509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>46258</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45770</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45915</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45636</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>46270</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45399</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45349</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44657</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>46275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45463</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44732</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>46255</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44888</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45478</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45490</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44735</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45205</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44515</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45573</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44972</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45665</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45799</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44664</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45575</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45589</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46076</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44515</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45113</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45618</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45961</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44806</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46282</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>46255</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45399</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45561</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45730</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45487</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44806</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>46062</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46085</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45618</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45492</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45461</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45834</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>44985</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46003</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46148</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46273</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45751</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46276</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>46252</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45399</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45523</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45205</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45206</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45821</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45105</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45736</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45573</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45874</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45586</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44494</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45526</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45622</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46072</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>46163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46210</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46097</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>46259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45936</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45589</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44619</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44810</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44859</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44533</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44817</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44616</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44619</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>44482</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44755</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>44805</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44545</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44495</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>44879</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44743</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44889</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44852</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44799</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44708</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44754</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45775</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44881</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44532</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>44923</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44837</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45154</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>44743</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45239</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45757</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45152</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45546</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45471</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45188</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45481</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45226</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45236</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44847</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45436</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44859</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45399</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44802</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45526</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45526</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44847</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44826</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45715</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45125</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45216</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45338</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45195</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45419</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45450</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45649</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44855</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45377</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45443</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45453</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45453</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45117</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45240</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45236</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45000</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45475</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45756</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44545</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44901</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45195</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45660</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>44847</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45442</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45883</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45463</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45883</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45526</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45883</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45883</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44972</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45229</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44881</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45884</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44977</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44658</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45478</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44852</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45884</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45884</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44914</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45730</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45730</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45545</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>44637</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45362</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45642</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45300</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45238</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45890</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45890</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45232</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45161</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44488</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45890</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45890</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45769</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44889</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44890</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45756</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45142</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45483</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45534</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45511</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45672</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45246</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45762</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45571</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45565</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45152</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45492</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45492</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44543</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>44515</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44515</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44522</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44977</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>44977</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44963</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45225</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>44911</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45403</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45541</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45777</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45161</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44949</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45545</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45636</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45643</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45316</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45779</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45656</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45558</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45915</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45560</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45399</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45216</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45205</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45207</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45216</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>45140</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45915</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45748</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44903</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45579</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45518</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45518</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>44917</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45408</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45555</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44515</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45516</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45516</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45232</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45548</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45792</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45791</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45582</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45433</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45331</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45147</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45793</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45518</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45376</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44693</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45485</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45149</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45526</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45048</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45343</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>44943</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45415</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45349</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>44981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45800</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45238</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45238</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44847</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45799</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45803</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45937</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45804</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45805</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45237</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45440</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44978</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45590</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45810</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45810</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45617</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45463</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45190</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45944</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>44994</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45222</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45762</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45636</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45636</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45636</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45625</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45944</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45435</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45541</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45541</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45573</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45280</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45084</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45817</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45429</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45730</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45817</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44686</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45254</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>45820</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45823</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45824</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45222</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>44923</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>44615</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45597</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45951</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45478</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45148</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45286,7 +45286,7 @@
         <v>45951</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>45831</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45225</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45618</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45951</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45954</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45954</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45957</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>44628</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45834</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45558</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45957</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45957</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45791</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45254</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45957</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45957</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45957</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>44972</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45957</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45957</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45957</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45840</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45508</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45636</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44747</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45092</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45278</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45841</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45636</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45408</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45469</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45971</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45202</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45158</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44743</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45847</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45756</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>45756</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45756</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45693</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45853</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45853</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45457</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45205</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45862</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44971</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45435</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45512</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45625</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>44640</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49758,7 +49758,7 @@
         <v>45478</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>45874</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45748</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45453</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45170</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45656</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45089</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>44522</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45874</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45874</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45660</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45660</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45297</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>45979</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45982</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45877</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45877</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>44826</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45981</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>45238</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45238</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45443</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45238</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45531</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>44657</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>45777</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45574</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45260</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>44522</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45985</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45090</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52126,7 +52126,7 @@
         <v>45730</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45730</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>44540</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>45985</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>46105</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45232</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45730</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45730</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45308</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>45415</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>44909</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>44903</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45769</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45524</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>46111</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>44628</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>46111</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>46113</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46113</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>45597</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45574</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         <v>45754</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>46113</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46121</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>45931</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45993</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45996</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46125</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46122</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46122</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46122</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>45999</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45622</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45495</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>44627</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>46001</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>44748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45635</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46129</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>46132</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>46132</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45378</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>46132</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>45442</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45526</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>44995</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>46006</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>44857</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45140</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45622</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45730</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>44657</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46129</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>45388</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>45000</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45428</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>45042</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>44488</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45847</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45692</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56822,7 +56822,7 @@
         <v>45251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56895,7 +56895,7 @@
         <v>45520</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45505</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>45552</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45993</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>44943</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45470</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45089</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>46038</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>45636</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45154</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45709</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>44957</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45992</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45000</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44963</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>44515</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45469</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>44972</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46045</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>44972</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44972</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58556,7 +58556,7 @@
         <v>46055</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>46055</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>46055</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>46055</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>46049</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45659</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>45625</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>46144</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>46066</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>45659</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59301,7 +59301,7 @@
         <v>45659</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45659</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46150</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>46149</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>46070</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46153</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45894</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44623</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>46157</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>46160</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45653</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>46093</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>44545</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>46162</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>46048</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>45993</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>44545</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>46163</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>46163</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>46168</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>46168</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>46168</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60962,7 +60962,7 @@
         <v>46171</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         <v>46174</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>46175</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>46087</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46174</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45297</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46181</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>46183</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46183</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>46183</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61722,7 +61722,7 @@
         <v>46183</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>46189</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>46191</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>46191</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>46184</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>45912</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62170,7 +62170,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46196</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>46199</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45972</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>45972</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62696,7 +62696,7 @@
         <v>46198</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>46199</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>45709</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46198</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>46205</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63076,7 +63076,7 @@
         <v>46204</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>46204</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>46205</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63305,7 +63305,7 @@
         <v>46204</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63383,7 +63383,7 @@
         <v>46204</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>46205</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>46204</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63612,7 +63612,7 @@
         <v>46205</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63685,7 +63685,7 @@
         <v>46209</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63763,7 +63763,7 @@
         <v>46209</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>46206</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>46209</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>46209</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>46206</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>46076</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>46209</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64304,7 +64304,7 @@
         <v>46210</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45876</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64450,7 +64450,7 @@
         <v>46210</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46217</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64596,7 +64596,7 @@
         <v>46038</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         <v>46213</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64742,7 +64742,7 @@
         <v>44686</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64820,7 +64820,7 @@
         <v>46213</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64893,7 +64893,7 @@
         <v>45953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>45979</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46267</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65117,7 +65117,7 @@
         <v>46273</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65195,7 +65195,7 @@
         <v>46276</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45734</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>46282</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>46282</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65570,7 +65570,7 @@
         <v>45989</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>45989</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>45989</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65804,7 +65804,7 @@
         <v>45989</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>45989</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>46085</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>46097</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>46281</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>46163</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>46240</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66330,7 +66330,7 @@
         <v>46240</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66408,7 +66408,7 @@
         <v>45786</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         <v>45786</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>46283</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>45813</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66705,7 +66705,7 @@
         <v>45996</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66778,7 +66778,7 @@
         <v>46272</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>46244</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66929,7 +66929,7 @@
         <v>46286</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>46076</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>46289</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>46157</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>46048</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46289</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67377,7 +67377,7 @@
         <v>46289</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67450,7 +67450,7 @@
         <v>46289</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67523,7 +67523,7 @@
         <v>45995</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67596,7 +67596,7 @@
         <v>46248</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>46265</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>46162</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>45989</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67893,7 +67893,7 @@
         <v>46252</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>46252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>46265</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>46252</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68190,7 +68190,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68263,7 +68263,7 @@
         <v>46252</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68336,7 +68336,7 @@
         <v>46252</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>46255</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68482,7 +68482,7 @@
         <v>46255</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68555,7 +68555,7 @@
         <v>46255</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68628,7 +68628,7 @@
         <v>46255</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>46104</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68779,7 +68779,7 @@
         <v>46255</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>46104</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68930,7 +68930,7 @@
         <v>46255</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69003,7 +69003,7 @@
         <v>46255</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69076,7 +69076,7 @@
         <v>46255</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69149,7 +69149,7 @@
         <v>46255</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69222,7 +69222,7 @@
         <v>46252</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>46301</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>46301</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>46301</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69529,7 +69529,7 @@
         <v>46258</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69607,7 +69607,7 @@
         <v>46301</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69680,7 +69680,7 @@
         <v>46301</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69753,7 +69753,7 @@
         <v>46301</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69831,7 +69831,7 @@
         <v>46301</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>46301</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>46301</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70060,7 +70060,7 @@
         <v>46304</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70133,7 +70133,7 @@
         <v>46304</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70206,7 +70206,7 @@
         <v>45583</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>45586</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>45587</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>45587</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70518,7 +70518,7 @@
         <v>45757</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45586</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70674,7 +70674,7 @@
         <v>45545</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70747,7 +70747,7 @@
         <v>46304</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         <v>45589</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70898,7 +70898,7 @@
         <v>46262</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45800</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71054,7 +71054,7 @@
         <v>46178</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71132,7 +71132,7 @@
         <v>46275</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71210,7 +71210,7 @@
         <v>44574</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71283,7 +71283,7 @@
         <v>44566</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71356,7 +71356,7 @@
         <v>44491</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71429,7 +71429,7 @@
         <v>45061</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71502,7 +71502,7 @@
         <v>45393</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45061</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>45393</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45061</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71794,7 +71794,7 @@
         <v>45393</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71867,7 +71867,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71945,7 +71945,7 @@
         <v>45932</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44972</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>44644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>44494</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45947</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>45154</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46141</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44881</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44972</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>46104</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>45989</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46142</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45734</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>44522</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45295</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>45561</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45989</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45716</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>45636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45399</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45113</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>46276</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45054</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>45509</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         <v>44945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>45764</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>46258</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45887</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>45770</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45051</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45915</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>45636</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45149</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>46073</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>45636</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45903</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>46270</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45399</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>45208</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7986,7 +7986,7 @@
         <v>45349</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>44657</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>46275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45205</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44964</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
         <v>44964</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>45238</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45463</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44732</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45644</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>46255</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         <v>45625</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>44888</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>45478</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>45497</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44698</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>45490</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44735</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>45205</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45764</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>44648</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>44515</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45573</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>44972</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45665</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45799</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44664</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>45575</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>45629</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
         <v>45589</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>46076</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>45546</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45552</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>45545</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45709</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45989</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>46286</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46076</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44515</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45113</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45278</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45618</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>45546</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45961</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44806</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>45545</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14033,7 +14033,7 @@
         <v>46282</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>46255</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>44529</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>45558</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45399</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>45561</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45730</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45487</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>44806</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>46062</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46093</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45545</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46085</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15824,7 +15824,7 @@
         <v>45936</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44603</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>45733</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45119</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>45883</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45618</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45492</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45541</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45461</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45817</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>45834</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44518</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45643</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>44985</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46003</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46148</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>45545</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>46268</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>46273</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45751</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46276</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>46252</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>46048</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45895</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19251,7 +19251,7 @@
         <v>44532</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45117</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45399</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45523</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45240</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>45205</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45206</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45821</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45105</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45515</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45736</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45573</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>45874</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>44852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45586</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>44494</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45254</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>45526</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45622</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>44560</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45541</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46072</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>46163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>46181</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46210</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>46097</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>46259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45936</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45589</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45439</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45469</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>46247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>44812</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44628</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44619</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>44619</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>44810</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44867</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>44859</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>44533</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>44844</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>44852</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>44712</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>44619</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>44817</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>44532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>44690</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>44858</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>44616</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44619</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -24965,7 +24965,7 @@
         <v>44617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>44482</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>44755</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>44805</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44545</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44532</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44495</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>44879</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>44743</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44743</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>44889</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44852</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>44799</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26120,7 +26120,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44708</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>44754</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45775</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>44881</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>44532</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>44923</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>44837</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45154</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>44743</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45239</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>45757</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         <v>45152</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45239</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27240,7 +27240,7 @@
         <v>45546</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>45471</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>45188</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45481</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45226</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45190</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45236</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>44847</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44847</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45436</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44859</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45399</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44802</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>45526</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>45526</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44847</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>45735</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>44826</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28594,7 +28594,7 @@
         <v>45715</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45125</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45216</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45338</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -28896,7 +28896,7 @@
         <v>45195</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -28974,7 +28974,7 @@
         <v>45419</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>45450</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45649</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>44855</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>45232</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45377</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45443</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>45048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29578,7 +29578,7 @@
         <v>45453</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>45453</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45509</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45117</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>45239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45240</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45236</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45166</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45000</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45475</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45756</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>44545</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>44901</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45195</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45660</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>44847</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>45442</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -30869,7 +30869,7 @@
         <v>45743</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -30942,7 +30942,7 @@
         <v>45883</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31098,7 +31098,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45463</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45883</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45526</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45883</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31478,7 +31478,7 @@
         <v>45883</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>44972</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45229</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>44881</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45884</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -31858,7 +31858,7 @@
         <v>44977</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>44658</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45278</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45478</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>44852</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45147</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45884</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45884</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>44914</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32545,7 +32545,7 @@
         <v>45730</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32623,7 +32623,7 @@
         <v>45730</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
         <v>45545</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32779,7 +32779,7 @@
         <v>44637</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32852,7 +32852,7 @@
         <v>45575</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -32930,7 +32930,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33076,7 +33076,7 @@
         <v>45362</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45642</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>44532</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45300</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>45238</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45890</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33607,7 +33607,7 @@
         <v>45890</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>44505</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45232</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>45161</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>44488</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45890</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45890</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45769</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>44889</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34289,7 +34289,7 @@
         <v>44890</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45756</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>44972</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45142</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45483</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45534</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34747,7 +34747,7 @@
         <v>45511</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45672</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45246</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>45762</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45571</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45571</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45565</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45152</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35429,7 +35429,7 @@
         <v>45492</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45492</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44543</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45148</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>44515</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>44515</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -35960,7 +35960,7 @@
         <v>45643</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>44522</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36116,7 +36116,7 @@
         <v>44977</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36194,7 +36194,7 @@
         <v>44977</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>44963</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45225</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>45524</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>44911</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45403</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45541</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45777</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45161</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>44949</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>45545</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45636</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>45643</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45316</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>45779</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>45656</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45558</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45915</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37583,7 +37583,7 @@
         <v>45560</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45399</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37734,7 +37734,7 @@
         <v>45216</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37807,7 +37807,7 @@
         <v>45205</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45206</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37963,7 +37963,7 @@
         <v>45207</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45216</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         <v>45140</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>45636</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38265,7 +38265,7 @@
         <v>45114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38343,7 +38343,7 @@
         <v>45915</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38416,7 +38416,7 @@
         <v>45748</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38489,7 +38489,7 @@
         <v>44903</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45579</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45518</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45518</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>44917</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45408</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45555</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44515</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39161,7 +39161,7 @@
         <v>45516</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39239,7 +39239,7 @@
         <v>45516</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39317,7 +39317,7 @@
         <v>45232</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39390,7 +39390,7 @@
         <v>45548</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45792</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>45791</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44568</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45582</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39775,7 +39775,7 @@
         <v>45433</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45331</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39921,7 +39921,7 @@
         <v>45147</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>45793</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45518</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45376</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40228,7 +40228,7 @@
         <v>45159</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40301,7 +40301,7 @@
         <v>44693</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40374,7 +40374,7 @@
         <v>45485</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40447,7 +40447,7 @@
         <v>45149</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40525,7 +40525,7 @@
         <v>45526</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45048</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40676,7 +40676,7 @@
         <v>45343</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40749,7 +40749,7 @@
         <v>44943</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>44735</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40900,7 +40900,7 @@
         <v>45415</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>45349</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41051,7 +41051,7 @@
         <v>44981</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41124,7 +41124,7 @@
         <v>45800</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>45238</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41358,7 +41358,7 @@
         <v>45238</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41436,7 +41436,7 @@
         <v>44847</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41509,7 +41509,7 @@
         <v>45799</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45803</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41665,7 +41665,7 @@
         <v>45937</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41743,7 +41743,7 @@
         <v>45804</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>45805</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41899,7 +41899,7 @@
         <v>45237</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>45096</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42050,7 +42050,7 @@
         <v>45636</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45440</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42201,7 +42201,7 @@
         <v>44978</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42274,7 +42274,7 @@
         <v>45590</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42347,7 +42347,7 @@
         <v>45810</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42425,7 +42425,7 @@
         <v>45810</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45617</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>45463</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45190</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42737,7 +42737,7 @@
         <v>45944</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>44994</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45222</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45762</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43049,7 +43049,7 @@
         <v>45636</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43127,7 +43127,7 @@
         <v>45636</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>45636</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45625</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45944</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43439,7 +43439,7 @@
         <v>45435</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45541</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45541</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43673,7 +43673,7 @@
         <v>45573</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45280</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45084</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43975,7 +43975,7 @@
         <v>45817</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45429</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45730</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45817</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44686</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44365,7 +44365,7 @@
         <v>45254</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>45820</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45823</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44672,7 +44672,7 @@
         <v>45824</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44750,7 +44750,7 @@
         <v>45222</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44828,7 +44828,7 @@
         <v>44923</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>44615</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45597</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45951</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>45478</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45148</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45286,7 +45286,7 @@
         <v>45951</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>45831</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45437,7 +45437,7 @@
         <v>45225</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45618</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45951</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45237</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>45957</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45822,7 +45822,7 @@
         <v>45954</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45954</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45957</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46051,7 +46051,7 @@
         <v>44628</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45834</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46280,7 +46280,7 @@
         <v>45558</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45833</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45957</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45957</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45957</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45791</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>45254</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46801,7 +46801,7 @@
         <v>45957</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45957</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>45957</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>44972</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45957</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45957</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>45957</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45957</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45840</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45508</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>45636</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>44747</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45092</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45278</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45841</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45206</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45636</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45408</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48150,7 +48150,7 @@
         <v>45469</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45971</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48306,7 +48306,7 @@
         <v>45202</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45158</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44743</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>45847</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>45756</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48691,7 +48691,7 @@
         <v>45756</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45756</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45693</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48915,7 +48915,7 @@
         <v>45853</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>45853</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49071,7 +49071,7 @@
         <v>45457</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45205</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49227,7 +49227,7 @@
         <v>45149</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49305,7 +49305,7 @@
         <v>45862</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49378,7 +49378,7 @@
         <v>44971</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>45435</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45512</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49607,7 +49607,7 @@
         <v>45625</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>44640</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49758,7 +49758,7 @@
         <v>45478</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49836,7 +49836,7 @@
         <v>45874</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>45748</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45453</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50065,7 +50065,7 @@
         <v>45170</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>45656</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50221,7 +50221,7 @@
         <v>45089</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50294,7 +50294,7 @@
         <v>44522</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50372,7 +50372,7 @@
         <v>45874</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45874</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45660</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45660</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50674,7 +50674,7 @@
         <v>45297</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50747,7 +50747,7 @@
         <v>45979</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45982</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50898,7 +50898,7 @@
         <v>45877</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>45877</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>44826</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45981</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>45238</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45238</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45443</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>45238</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51517,7 +51517,7 @@
         <v>45531</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51595,7 +51595,7 @@
         <v>44657</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51668,7 +51668,7 @@
         <v>45777</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>45574</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45260</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51892,7 +51892,7 @@
         <v>44522</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45985</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52048,7 +52048,7 @@
         <v>45090</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52126,7 +52126,7 @@
         <v>45730</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52204,7 +52204,7 @@
         <v>45730</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>44540</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52355,7 +52355,7 @@
         <v>45985</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52428,7 +52428,7 @@
         <v>46105</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52506,7 +52506,7 @@
         <v>45232</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52579,7 +52579,7 @@
         <v>45730</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52657,7 +52657,7 @@
         <v>45730</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
         <v>45308</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52808,7 +52808,7 @@
         <v>45415</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52881,7 +52881,7 @@
         <v>44909</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>44903</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53027,7 +53027,7 @@
         <v>45769</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45524</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53183,7 +53183,7 @@
         <v>46111</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>44628</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53334,7 +53334,7 @@
         <v>46111</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>46113</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46113</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53568,7 +53568,7 @@
         <v>45597</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45574</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53719,7 +53719,7 @@
         <v>45754</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53797,7 +53797,7 @@
         <v>45390</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53875,7 +53875,7 @@
         <v>46113</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53953,7 +53953,7 @@
         <v>46121</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54031,7 +54031,7 @@
         <v>45931</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54104,7 +54104,7 @@
         <v>45993</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54177,7 +54177,7 @@
         <v>45996</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54250,7 +54250,7 @@
         <v>46125</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54328,7 +54328,7 @@
         <v>46122</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>46122</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>46122</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>45999</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54620,7 +54620,7 @@
         <v>45622</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54693,7 +54693,7 @@
         <v>45495</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54771,7 +54771,7 @@
         <v>44627</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54844,7 +54844,7 @@
         <v>46001</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>44748</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45635</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46129</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55151,7 +55151,7 @@
         <v>46132</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>46132</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45378</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>46132</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55458,7 +55458,7 @@
         <v>45442</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55536,7 +55536,7 @@
         <v>45526</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55614,7 +55614,7 @@
         <v>44995</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>46006</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>44857</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45140</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45622</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45730</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>45225</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>44657</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>46129</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>45388</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>45000</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56442,7 +56442,7 @@
         <v>45428</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56520,7 +56520,7 @@
         <v>45042</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56598,7 +56598,7 @@
         <v>44488</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56671,7 +56671,7 @@
         <v>45847</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>45692</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56822,7 +56822,7 @@
         <v>45251</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56895,7 +56895,7 @@
         <v>45520</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56973,7 +56973,7 @@
         <v>45505</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57046,7 +57046,7 @@
         <v>45478</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>45552</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57202,7 +57202,7 @@
         <v>45993</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57275,7 +57275,7 @@
         <v>44943</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57348,7 +57348,7 @@
         <v>45470</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57426,7 +57426,7 @@
         <v>45089</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         <v>46038</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57577,7 +57577,7 @@
         <v>45636</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45154</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45709</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>44957</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45992</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>45000</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>44963</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>44515</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45469</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58244,7 +58244,7 @@
         <v>44972</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46045</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58400,7 +58400,7 @@
         <v>44972</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58478,7 +58478,7 @@
         <v>44972</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58556,7 +58556,7 @@
         <v>46055</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58629,7 +58629,7 @@
         <v>46055</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>46055</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>46055</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>46049</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45659</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>45625</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59077,7 +59077,7 @@
         <v>46144</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59150,7 +59150,7 @@
         <v>46066</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>45659</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59301,7 +59301,7 @@
         <v>45659</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45659</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>46150</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>46149</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>46070</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59671,7 +59671,7 @@
         <v>46153</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59749,7 +59749,7 @@
         <v>45894</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59822,7 +59822,7 @@
         <v>44623</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59900,7 +59900,7 @@
         <v>46157</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59978,7 +59978,7 @@
         <v>46160</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60051,7 +60051,7 @@
         <v>45653</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>46093</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60207,7 +60207,7 @@
         <v>44545</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60280,7 +60280,7 @@
         <v>46162</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60353,7 +60353,7 @@
         <v>46048</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60426,7 +60426,7 @@
         <v>45993</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60499,7 +60499,7 @@
         <v>44545</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60572,7 +60572,7 @@
         <v>46163</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60650,7 +60650,7 @@
         <v>46163</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>46168</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60806,7 +60806,7 @@
         <v>46168</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60884,7 +60884,7 @@
         <v>46168</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60962,7 +60962,7 @@
         <v>46171</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61035,7 +61035,7 @@
         <v>46174</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>46175</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>46087</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>46174</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>45297</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>46181</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61493,7 +61493,7 @@
         <v>46183</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61571,7 +61571,7 @@
         <v>46183</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>46183</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61722,7 +61722,7 @@
         <v>46183</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>46189</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>46191</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>46191</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62019,7 +62019,7 @@
         <v>46184</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>45912</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62170,7 +62170,7 @@
         <v>46196</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46196</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62326,7 +62326,7 @@
         <v>46199</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62399,7 +62399,7 @@
         <v>45972</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>45972</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>46198</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62623,7 +62623,7 @@
         <v>46198</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62696,7 +62696,7 @@
         <v>46198</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62774,7 +62774,7 @@
         <v>46199</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62852,7 +62852,7 @@
         <v>45709</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>46198</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>46205</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63076,7 +63076,7 @@
         <v>46204</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>46204</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>46205</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63305,7 +63305,7 @@
         <v>46204</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63383,7 +63383,7 @@
         <v>46204</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>46205</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63534,7 +63534,7 @@
         <v>46204</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63612,7 +63612,7 @@
         <v>46205</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63685,7 +63685,7 @@
         <v>46209</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63763,7 +63763,7 @@
         <v>46209</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>46206</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63919,7 +63919,7 @@
         <v>46209</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63997,7 +63997,7 @@
         <v>46209</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64075,7 +64075,7 @@
         <v>46206</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64153,7 +64153,7 @@
         <v>46076</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>46209</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64304,7 +64304,7 @@
         <v>46210</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64377,7 +64377,7 @@
         <v>45876</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64450,7 +64450,7 @@
         <v>46210</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64523,7 +64523,7 @@
         <v>46217</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64596,7 +64596,7 @@
         <v>46038</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         <v>46213</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64742,7 +64742,7 @@
         <v>44686</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64820,7 +64820,7 @@
         <v>46213</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64893,7 +64893,7 @@
         <v>45953</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64966,7 +64966,7 @@
         <v>45979</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>46267</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65117,7 +65117,7 @@
         <v>46273</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65195,7 +65195,7 @@
         <v>46276</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65268,7 +65268,7 @@
         <v>46276</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65341,7 +65341,7 @@
         <v>45734</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65414,7 +65414,7 @@
         <v>46282</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>46282</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65570,7 +65570,7 @@
         <v>45989</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65648,7 +65648,7 @@
         <v>45989</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65726,7 +65726,7 @@
         <v>45989</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65804,7 +65804,7 @@
         <v>45989</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65882,7 +65882,7 @@
         <v>45989</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>46085</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66033,7 +66033,7 @@
         <v>46097</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66106,7 +66106,7 @@
         <v>46281</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66179,7 +66179,7 @@
         <v>46163</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66252,7 +66252,7 @@
         <v>46240</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66330,7 +66330,7 @@
         <v>46240</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66408,7 +66408,7 @@
         <v>45786</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66481,7 +66481,7 @@
         <v>45786</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66554,7 +66554,7 @@
         <v>46283</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66627,7 +66627,7 @@
         <v>45813</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66705,7 +66705,7 @@
         <v>45996</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66778,7 +66778,7 @@
         <v>46272</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66851,7 +66851,7 @@
         <v>46244</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66929,7 +66929,7 @@
         <v>46286</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>46076</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>46289</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>46157</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67231,7 +67231,7 @@
         <v>46048</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67304,7 +67304,7 @@
         <v>46289</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67377,7 +67377,7 @@
         <v>46289</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67450,7 +67450,7 @@
         <v>46289</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67523,7 +67523,7 @@
         <v>45995</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67596,7 +67596,7 @@
         <v>46248</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>46265</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>46162</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>45989</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67893,7 +67893,7 @@
         <v>46252</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>46252</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>46265</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>46252</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68190,7 +68190,7 @@
         <v>46252</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68263,7 +68263,7 @@
         <v>46252</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68336,7 +68336,7 @@
         <v>46252</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>46255</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68482,7 +68482,7 @@
         <v>46255</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68555,7 +68555,7 @@
         <v>46255</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68628,7 +68628,7 @@
         <v>46255</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>46104</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68779,7 +68779,7 @@
         <v>46255</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>46104</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68930,7 +68930,7 @@
         <v>46255</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69003,7 +69003,7 @@
         <v>46255</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69076,7 +69076,7 @@
         <v>46255</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69149,7 +69149,7 @@
         <v>46255</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69222,7 +69222,7 @@
         <v>46252</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69300,7 +69300,7 @@
         <v>46301</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69373,7 +69373,7 @@
         <v>46301</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69451,7 +69451,7 @@
         <v>46301</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69529,7 +69529,7 @@
         <v>46258</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69607,7 +69607,7 @@
         <v>46301</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69680,7 +69680,7 @@
         <v>46301</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69753,7 +69753,7 @@
         <v>46301</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69831,7 +69831,7 @@
         <v>46301</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69909,7 +69909,7 @@
         <v>46301</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69982,7 +69982,7 @@
         <v>46301</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70060,7 +70060,7 @@
         <v>46304</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70133,7 +70133,7 @@
         <v>46304</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70206,7 +70206,7 @@
         <v>45583</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70284,7 +70284,7 @@
         <v>45586</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70362,7 +70362,7 @@
         <v>45587</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70440,7 +70440,7 @@
         <v>45587</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70518,7 +70518,7 @@
         <v>45757</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70596,7 +70596,7 @@
         <v>45586</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70674,7 +70674,7 @@
         <v>45545</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70747,7 +70747,7 @@
         <v>46304</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         <v>45589</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70898,7 +70898,7 @@
         <v>46262</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70976,7 +70976,7 @@
         <v>45800</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71054,7 +71054,7 @@
         <v>46178</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71132,7 +71132,7 @@
         <v>46275</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71210,7 +71210,7 @@
         <v>44574</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71283,7 +71283,7 @@
         <v>44566</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71356,7 +71356,7 @@
         <v>44491</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71429,7 +71429,7 @@
         <v>45061</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71502,7 +71502,7 @@
         <v>45393</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>45061</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>45393</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45061</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71794,7 +71794,7 @@
         <v>45393</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71867,7 +71867,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71945,7 +71945,7 @@
         <v>45932</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44972</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>44644</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44838</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44494</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>44881</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>45625</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45989</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45583</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46276</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>46142</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44972</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44522</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45561</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45989</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45295</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45716</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45478</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>45636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45399</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>45113</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45509</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
         <v>44945</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>45764</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>46258</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45887</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>45770</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45399</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>45915</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45636</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>45149</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>45051</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>46073</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45636</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>46270</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>44657</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45349</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>46275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>46097</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45205</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45399</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44964</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45463</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>46058</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45238</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44732</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>45644</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>46255</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45625</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44735</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45490</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>44698</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>45205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45764</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44888</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>45478</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44648</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>45573</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>45589</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44664</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44972</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>46076</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11899,7 +11899,7 @@
         <v>44515</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45665</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45799</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45546</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45188</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45552</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45545</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>45709</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45989</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>46009</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>46076</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>46286</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44515</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45461</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45546</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45961</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45957</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>44806</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>45618</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45278</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45113</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45545</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>46282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14527,7 +14527,7 @@
         <v>46255</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>46080</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45730</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>45558</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45561</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45399</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>44806</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44529</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45478</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45560</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>46062</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45545</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45487</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46085</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>44603</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45733</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45643</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45461</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>44518</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>46148</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45937</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45625</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>46003</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45618</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>44985</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18103,7 +18103,7 @@
         <v>46273</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18319,7 +18319,7 @@
         <v>46162</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46276</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45541</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>46252</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>46048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45492</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46268</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45817</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45834</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45895</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>46093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44518</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>44532</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>44852</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         <v>45526</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>45105</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>45240</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45206</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45117</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>44911</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20628,7 +20628,7 @@
         <v>45936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         <v>45541</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>44560</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>46072</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45515</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45736</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45540</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45586</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21618,7 +21618,7 @@
         <v>44494</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45582</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45523</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>46181</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>45622</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>46210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45573</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>45205</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46097</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45399</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>46259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
         <v>45804</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23039,7 +23039,7 @@
         <v>46163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45936</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45589</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>45821</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45874</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>45439</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45469</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>46247</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>44812</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         <v>44628</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>44619</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>44810</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>44859</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>44867</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>44533</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44628</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24513,7 +24513,7 @@
         <v>44619</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         <v>44844</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>44852</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24742,7 +24742,7 @@
         <v>44712</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24820,7 +24820,7 @@
         <v>44619</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>44532</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -24966,7 +24966,7 @@
         <v>44817</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44690</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>44858</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>44743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>44889</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>44754</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>44619</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>44616</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>44755</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>44532</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>44743</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>44743</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>44852</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44708</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44532</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>44805</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26355,7 +26355,7 @@
         <v>44879</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>44799</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>44617</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>44545</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44495</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44837</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>44743</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44972</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45471</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>45597</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45481</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45560</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44914</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27354,7 +27354,7 @@
         <v>44545</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45470</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45660</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45048</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>44657</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45518</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>45643</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45140</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45254</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45541</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45541</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>44889</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>45237</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28479,7 +28479,7 @@
         <v>44627</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45478</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45238</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>45571</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44901</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28854,7 +28854,7 @@
         <v>45571</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>44923</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>44942</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45693</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>44515</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>44522</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         <v>45166</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45114</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29453,7 +29453,7 @@
         <v>45202</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44748</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45237</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45555</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45512</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45239</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44802</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>45730</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30223,7 +30223,7 @@
         <v>45730</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>45573</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45526</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30452,7 +30452,7 @@
         <v>45526</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>44971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45469</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44568</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45656</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>45338</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45597</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>44852</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45239</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45195</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45238</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>45238</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         <v>45308</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         <v>45259</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31587,7 +31587,7 @@
         <v>44515</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44515</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45579</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45672</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31879,7 +31879,7 @@
         <v>44826</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>44847</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44522</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32108,7 +32108,7 @@
         <v>45730</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>45730</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32264,7 +32264,7 @@
         <v>45240</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45463</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44505</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32493,7 +32493,7 @@
         <v>45636</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>45656</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>45730</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>45730</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44847</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45463</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33034,7 +33034,7 @@
         <v>45590</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33107,7 +33107,7 @@
         <v>45280</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>45495</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45226</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>45618</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>45883</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>45343</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45884</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33638,7 +33638,7 @@
         <v>45847</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33711,7 +33711,7 @@
         <v>45505</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>45769</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>44981</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>45170</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45735</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45216</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>45483</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>44543</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>44963</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45890</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45884</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34554,7 +34554,7 @@
         <v>45890</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34632,7 +34632,7 @@
         <v>45260</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45890</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34783,7 +34783,7 @@
         <v>45890</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>44855</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34939,7 +34939,7 @@
         <v>45884</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>44890</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45388</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>45659</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45692</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44540</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45125</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45403</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45161</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44957</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35689,7 +35689,7 @@
         <v>45408</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45915</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35835,7 +35835,7 @@
         <v>45915</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35908,7 +35908,7 @@
         <v>45757</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45206</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45558</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>46144</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>44488</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>44972</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>46149</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45331</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45574</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36663,7 +36663,7 @@
         <v>46153</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>46150</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>45775</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45546</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>45238</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45642</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45937</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45089</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>45636</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37345,7 +37345,7 @@
         <v>45399</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45625</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45636</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45636</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44977</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45944</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37803,7 +37803,7 @@
         <v>45944</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37881,7 +37881,7 @@
         <v>45894</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45951</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45951</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38100,7 +38100,7 @@
         <v>45951</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38173,7 +38173,7 @@
         <v>45415</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45229</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>44515</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45954</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45954</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>45957</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>45957</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44623</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38777,7 +38777,7 @@
         <v>46157</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38855,7 +38855,7 @@
         <v>45653</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>45643</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39011,7 +39011,7 @@
         <v>45558</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45508</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
         <v>45957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45957</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45142</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45957</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>45957</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45957</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45957</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>45957</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>45957</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>45957</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>45435</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>45993</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40048,7 +40048,7 @@
         <v>45216</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>46048</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>44545</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40272,7 +40272,7 @@
         <v>45636</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>44972</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45971</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40506,7 +40506,7 @@
         <v>46162</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45161</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46163</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44545</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45715</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40886,7 +40886,7 @@
         <v>44658</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40959,7 +40959,7 @@
         <v>45625</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41037,7 +41037,7 @@
         <v>45636</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>45979</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44847</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44847</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>46163</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41412,7 +41412,7 @@
         <v>45981</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         <v>45762</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41563,7 +41563,7 @@
         <v>45754</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>45985</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45985</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45000</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>44917</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>45982</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42016,7 +42016,7 @@
         <v>45478</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>45225</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46168</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>46168</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>46168</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>44911</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42557,7 +42557,7 @@
         <v>45996</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45195</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45999</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44972</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45478</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>46001</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         <v>45622</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>44994</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>44943</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45297</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43385,7 +43385,7 @@
         <v>45232</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>44657</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45436</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45089</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>46174</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45442</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>45216</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46174</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>45478</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>46171</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>45435</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44218,7 +44218,7 @@
         <v>45399</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>45622</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45232</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45188</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45428</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44593,7 +44593,7 @@
         <v>46087</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45574</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>46175</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>45457</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44900,7 +44900,7 @@
         <v>45552</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44978,7 +44978,7 @@
         <v>45636</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45056,7 +45056,7 @@
         <v>46038</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45582</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45212,7 +45212,7 @@
         <v>45408</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45453</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45363,7 +45363,7 @@
         <v>45443</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45441,7 +45441,7 @@
         <v>44881</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>46045</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45592,7 +45592,7 @@
         <v>46181</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         <v>45756</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45748,7 +45748,7 @@
         <v>45207</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45826,7 +45826,7 @@
         <v>45225</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>46055</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>46055</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>46055</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>46055</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46196,7 +46196,7 @@
         <v>46183</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46269,7 +46269,7 @@
         <v>45625</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>45148</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45205</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>46049</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46576,7 +46576,7 @@
         <v>46183</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>45236</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>46183</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46810,7 +46810,7 @@
         <v>46189</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45659</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45659</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47029,7 +47029,7 @@
         <v>45659</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47102,7 +47102,7 @@
         <v>44903</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47175,7 +47175,7 @@
         <v>45222</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>46066</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>45429</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>46070</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47482,7 +47482,7 @@
         <v>45617</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47560,7 +47560,7 @@
         <v>44637</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>45475</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>45526</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45246</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45149</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>46184</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45152</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45148</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48174,7 +48174,7 @@
         <v>46093</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48252,7 +48252,7 @@
         <v>46191</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48330,7 +48330,7 @@
         <v>46191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45511</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45777</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45526</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48632,7 +48632,7 @@
         <v>45509</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48710,7 +48710,7 @@
         <v>46196</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>46196</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48866,7 +48866,7 @@
         <v>46105</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>44532</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>44995</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49095,7 +49095,7 @@
         <v>45912</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45239</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>46198</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>46198</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>44881</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>45972</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45972</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>46111</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>46111</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>46198</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46198</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46113</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>46113</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45756</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45756</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45756</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>46113</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45931</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>45565</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>44972</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>46199</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>46122</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>46122</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45709</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>46122</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>46121</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>46125</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51126,7 +51126,7 @@
         <v>45635</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>46129</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         <v>46199</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>46132</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>46132</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45159</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>46132</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51662,7 +51662,7 @@
         <v>45190</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46204</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>46205</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>45297</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>46129</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>44972</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52120,7 +52120,7 @@
         <v>46204</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>46204</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52276,7 +52276,7 @@
         <v>45117</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>46204</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>44628</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45251</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45992</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45709</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>46204</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45485</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45518</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>45092</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45545</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>46206</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45238</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45238</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>45993</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53416,7 +53416,7 @@
         <v>45376</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>46076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>45206</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53640,7 +53640,7 @@
         <v>45225</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53718,7 +53718,7 @@
         <v>46206</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53796,7 +53796,7 @@
         <v>44522</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53874,7 +53874,7 @@
         <v>46205</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53947,7 +53947,7 @@
         <v>45084</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54025,7 +54025,7 @@
         <v>45154</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>45492</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>45492</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54259,7 +54259,7 @@
         <v>45469</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>46205</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>46205</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>46209</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54561,7 +54561,7 @@
         <v>46209</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>46210</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54712,7 +54712,7 @@
         <v>46209</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54790,7 +54790,7 @@
         <v>46210</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54863,7 +54863,7 @@
         <v>46209</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54941,7 +54941,7 @@
         <v>45090</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>46209</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55097,7 +55097,7 @@
         <v>45541</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55175,7 +55175,7 @@
         <v>45876</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55248,7 +55248,7 @@
         <v>46038</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55321,7 +55321,7 @@
         <v>45152</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>45236</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>45450</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45278</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>46213</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>44686</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>46217</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55847,7 +55847,7 @@
         <v>46213</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55920,7 +55920,7 @@
         <v>45756</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45748</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>45953</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>44743</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>44972</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>44826</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>45000</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>44943</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>45300</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56592,7 +56592,7 @@
         <v>44628</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56665,7 +56665,7 @@
         <v>45042</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>46273</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>45222</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>44923</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>45419</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45524</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57128,7 +57128,7 @@
         <v>44564</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57201,7 +57201,7 @@
         <v>46276</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57274,7 +57274,7 @@
         <v>46276</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57347,7 +57347,7 @@
         <v>44977</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57425,7 +57425,7 @@
         <v>44977</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57503,7 +57503,7 @@
         <v>44857</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57576,7 +57576,7 @@
         <v>46281</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57649,7 +57649,7 @@
         <v>45349</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57722,7 +57722,7 @@
         <v>44615</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57795,7 +57795,7 @@
         <v>45989</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>45989</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57951,7 +57951,7 @@
         <v>45989</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58029,7 +58029,7 @@
         <v>45989</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58107,7 +58107,7 @@
         <v>46085</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58180,7 +58180,7 @@
         <v>45989</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46097</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>46163</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46282</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58482,7 +58482,7 @@
         <v>46282</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58560,7 +58560,7 @@
         <v>44735</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58638,7 +58638,7 @@
         <v>44488</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58711,7 +58711,7 @@
         <v>45453</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58789,7 +58789,7 @@
         <v>45453</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>46240</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46240</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59023,7 +59023,7 @@
         <v>45730</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45730</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>46283</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>45769</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59330,7 +59330,7 @@
         <v>45996</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59403,7 +59403,7 @@
         <v>46286</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59481,7 +59481,7 @@
         <v>46244</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45813</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59637,7 +59637,7 @@
         <v>45524</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59715,7 +59715,7 @@
         <v>45238</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59793,7 +59793,7 @@
         <v>45575</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>46272</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>45520</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60022,7 +60022,7 @@
         <v>45786</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45786</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60168,7 +60168,7 @@
         <v>45254</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60246,7 +60246,7 @@
         <v>45743</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>44903</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>45748</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>46289</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>44859</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45316</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60689,7 +60689,7 @@
         <v>45390</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60767,7 +60767,7 @@
         <v>44640</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60840,7 +60840,7 @@
         <v>46289</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60913,7 +60913,7 @@
         <v>45278</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60991,7 +60991,7 @@
         <v>45147</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>46289</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61142,7 +61142,7 @@
         <v>46289</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61215,7 +61215,7 @@
         <v>45534</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>46157</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61371,7 +61371,7 @@
         <v>45362</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45526</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45232</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61595,7 +61595,7 @@
         <v>45377</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61673,7 +61673,7 @@
         <v>44972</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61751,7 +61751,7 @@
         <v>45516</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61829,7 +61829,7 @@
         <v>45660</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45660</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>46048</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62048,7 +62048,7 @@
         <v>45995</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62121,7 +62121,7 @@
         <v>45048</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62194,7 +62194,7 @@
         <v>46248</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62272,7 +62272,7 @@
         <v>44747</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>46076</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>46252</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62496,7 +62496,7 @@
         <v>46252</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62574,7 +62574,7 @@
         <v>46252</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62647,7 +62647,7 @@
         <v>45516</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62725,7 +62725,7 @@
         <v>45516</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         <v>45762</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>44963</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62954,7 +62954,7 @@
         <v>46252</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63027,7 +63027,7 @@
         <v>45099</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63105,7 +63105,7 @@
         <v>45154</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>46252</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63251,7 +63251,7 @@
         <v>46252</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63324,7 +63324,7 @@
         <v>45158</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63397,7 +63397,7 @@
         <v>45649</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63470,7 +63470,7 @@
         <v>44693</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63543,7 +63543,7 @@
         <v>46265</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63616,7 +63616,7 @@
         <v>46255</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63689,7 +63689,7 @@
         <v>46255</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63762,7 +63762,7 @@
         <v>44909</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63835,7 +63835,7 @@
         <v>45378</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45442</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>45989</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64059,7 +64059,7 @@
         <v>46162</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         <v>46255</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64205,7 +64205,7 @@
         <v>46255</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>46252</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>46255</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>46255</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>46255</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>46301</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>46301</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64731,7 +64731,7 @@
         <v>45777</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64809,7 +64809,7 @@
         <v>46301</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64887,7 +64887,7 @@
         <v>44949</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64960,7 +64960,7 @@
         <v>45779</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65038,7 +65038,7 @@
         <v>46301</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65111,7 +65111,7 @@
         <v>46301</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65184,7 +65184,7 @@
         <v>46255</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>46258</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65335,7 +65335,7 @@
         <v>46255</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>46301</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>46301</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45216</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45140</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>46301</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65778,7 +65778,7 @@
         <v>46301</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>45545</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>45791</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>45433</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45793</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45548</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>46304</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66309,7 +66309,7 @@
         <v>45792</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66387,7 +66387,7 @@
         <v>46262</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66465,7 +66465,7 @@
         <v>45518</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66543,7 +66543,7 @@
         <v>45147</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66621,7 +66621,7 @@
         <v>45799</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66699,7 +66699,7 @@
         <v>45734</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66772,7 +66772,7 @@
         <v>45149</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66850,7 +66850,7 @@
         <v>46304</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66923,7 +66923,7 @@
         <v>46304</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66996,7 +66996,7 @@
         <v>46183</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67069,7 +67069,7 @@
         <v>46275</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67147,7 +67147,7 @@
         <v>45415</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67225,7 +67225,7 @@
         <v>45803</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67303,7 +67303,7 @@
         <v>44847</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67376,7 +67376,7 @@
         <v>45800</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67454,7 +67454,7 @@
         <v>45800</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67532,7 +67532,7 @@
         <v>45096</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67605,7 +67605,7 @@
         <v>45636</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67683,7 +67683,7 @@
         <v>45804</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>45440</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>45805</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67912,7 +67912,7 @@
         <v>45810</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67990,7 +67990,7 @@
         <v>45810</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68068,7 +68068,7 @@
         <v>44978</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68141,7 +68141,7 @@
         <v>45757</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68219,7 +68219,7 @@
         <v>46267</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68297,7 +68297,7 @@
         <v>45586</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68375,7 +68375,7 @@
         <v>45800</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68453,7 +68453,7 @@
         <v>45979</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68526,7 +68526,7 @@
         <v>46178</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68604,7 +68604,7 @@
         <v>45587</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68682,7 +68682,7 @@
         <v>45817</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68760,7 +68760,7 @@
         <v>45817</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68838,7 +68838,7 @@
         <v>44686</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68916,7 +68916,7 @@
         <v>45587</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68994,7 +68994,7 @@
         <v>45589</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69072,7 +69072,7 @@
         <v>45586</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69150,7 +69150,7 @@
         <v>45583</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69228,7 +69228,7 @@
         <v>45820</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69306,7 +69306,7 @@
         <v>45824</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69384,7 +69384,7 @@
         <v>45824</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69462,7 +69462,7 @@
         <v>46265</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69535,7 +69535,7 @@
         <v>45831</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69613,7 +69613,7 @@
         <v>45833</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69686,7 +69686,7 @@
         <v>45834</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69764,7 +69764,7 @@
         <v>45791</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69842,7 +69842,7 @@
         <v>45841</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69920,7 +69920,7 @@
         <v>45840</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69993,7 +69993,7 @@
         <v>45847</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70071,7 +70071,7 @@
         <v>45853</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70149,7 +70149,7 @@
         <v>45853</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70227,7 +70227,7 @@
         <v>45205</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70305,7 +70305,7 @@
         <v>45862</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         <v>45874</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70456,7 +70456,7 @@
         <v>45874</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70534,7 +70534,7 @@
         <v>45874</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70612,7 +70612,7 @@
         <v>45877</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70690,7 +70690,7 @@
         <v>45877</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70768,7 +70768,7 @@
         <v>45443</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70846,7 +70846,7 @@
         <v>45883</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70924,7 +70924,7 @@
         <v>45883</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71002,7 +71002,7 @@
         <v>45883</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71075,7 +71075,7 @@
         <v>45883</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71148,7 +71148,7 @@
         <v>44574</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71221,7 +71221,7 @@
         <v>44491</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71294,7 +71294,7 @@
         <v>44566</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71367,7 +71367,7 @@
         <v>45061</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71440,7 +71440,7 @@
         <v>45393</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71513,7 +71513,7 @@
         <v>45061</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71586,7 +71586,7 @@
         <v>45393</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71659,7 +71659,7 @@
         <v>45061</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71732,7 +71732,7 @@
         <v>45393</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71805,7 +71805,7 @@
         <v>45748</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71883,7 +71883,7 @@
         <v>45932</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44838</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44972</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44494</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44881</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45989</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45583</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44522</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45561</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45716</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45989</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46270</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45399</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45509</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>46258</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44945</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45770</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45915</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45636</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45149</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45399</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45903</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>46265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>46265</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44657</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>46097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>46275</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45349</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>46058</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45463</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45644</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>46255</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45625</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45490</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44648</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44515</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44972</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45665</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46076</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45575</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45589</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45709</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45989</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46009</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46286</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45957</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45961</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45545</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45278</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>46282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>46255</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45618</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>46080</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45461</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>44806</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45478</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45560</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44529</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45730</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45399</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45487</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44603</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45733</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45937</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45492</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46003</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45751</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>46276</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45817</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46252</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45834</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>46048</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45618</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46268</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>46273</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46148</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45545</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>44518</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45643</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44985</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>46093</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44518</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44532</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44911</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45541</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>46072</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45399</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45117</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45523</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45515</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45736</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45205</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45540</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46210</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46097</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45804</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45821</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45622</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>44560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45206</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45526</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44852</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>46247</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44812</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44628</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44619</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44619</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>44810</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44867</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44859</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44628</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44844</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44852</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44712</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44619</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44817</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44532</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44690</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44858</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>44743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44889</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44754</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44619</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>44532</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44852</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>44708</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44879</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44799</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44495</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44995</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>44837</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45883</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44743</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>44857</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45471</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45883</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45735</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44826</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45890</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45890</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45715</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45883</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45890</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45140</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45622</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45225</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45509</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44657</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>44890</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45884</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45775</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44881</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45428</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45042</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45884</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45884</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46157</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45653</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45403</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>46162</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>46048</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45993</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44545</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46163</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45478</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45636</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>46163</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>46168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44943</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45470</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45089</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46168</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45331</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46171</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45000</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46174</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44963</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44515</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46175</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45469</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>46087</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45236</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>44847</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45436</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44859</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45399</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44972</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46174</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44802</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45944</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44847</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45636</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45636</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45636</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45625</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45419</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45450</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45188</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>44855</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45232</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45377</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45443</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45453</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45453</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45526</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45526</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45951</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45951</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45125</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>46183</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>46183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45649</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45957</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45954</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45957</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45558</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45957</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46189</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45957</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45957</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45508</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46191</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45236</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45475</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>46184</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45195</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45636</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45442</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45743</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45971</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>46196</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46199</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46198</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>46199</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44977</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44658</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45625</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45709</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45730</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45730</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45979</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45982</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45981</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45362</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45642</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46205</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45463</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46204</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>46204</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>46205</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39438,7 +39438,7 @@
         <v>45985</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46205</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45985</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>46205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46206</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45769</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44889</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46209</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45756</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>46076</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45526</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46209</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45142</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45672</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45762</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45876</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>46210</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>44972</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45565</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45996</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45643</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46217</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45999</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46213</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44881</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>45225</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44686</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>46213</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45622</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45953</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46001</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45278</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45478</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45777</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44949</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45779</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45216</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44852</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>46282</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>46282</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45989</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45989</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45989</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45989</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>46085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>46097</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>46281</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>46163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45548</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45792</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45791</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45552</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45433</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45786</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45786</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45147</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>46038</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45793</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45518</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45813</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45996</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>46244</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45415</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>46045</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45800</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46076</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45800</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>44847</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45799</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46289</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46157</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46122,7 +46122,7 @@
         <v>46048</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45803</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45545</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45804</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>46055</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>46289</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45805</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>45096</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45636</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45440</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46055</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>46055</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44978</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46055</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45810</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45810</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46049</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45625</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>46066</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45659</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45659</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45817</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         <v>45659</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>46070</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45300</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>46248</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48221,7 +48221,7 @@
         <v>45817</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>44686</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45820</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46162</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45238</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48606,7 +48606,7 @@
         <v>45824</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         <v>45824</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45989</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>46252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
         <v>46252</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>46252</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45831</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>46252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>46252</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>46255</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>46255</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45834</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45833</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>46255</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45791</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45840</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>46093</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45161</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45777</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46255</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45841</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>46255</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>46255</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>46252</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>46105</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45847</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>46301</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>46301</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>46258</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>46301</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>46301</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>44972</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46301</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>45853</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>46301</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45853</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45483</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45205</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45534</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         <v>46111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46113</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46301</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>45862</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>46113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>46304</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45511</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>46113</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>46304</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>45246</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>45545</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>46121</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>46304</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>45874</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>46125</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>46122</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46122</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>46122</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>45099</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45874</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45874</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45877</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>44515</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>44515</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45877</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>46129</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45443</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46132</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>44972</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>44911</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>45734</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54676,7 +54676,7 @@
         <v>45883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>46183</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45541</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45545</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         <v>45560</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45205</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45207</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45216</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45800</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45586</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45587</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>46178</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45589</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45587</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46129</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>44903</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>45388</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45518</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56299,7 +56299,7 @@
         <v>45518</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>46267</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>44917</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45583</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45408</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56679,7 +56679,7 @@
         <v>45847</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>46314</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45692</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>45586</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45251</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45505</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45757</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45993</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>44568</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45912</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45709</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>44957</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>45992</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45979</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>46272</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46315</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>44693</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>46318</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45972</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>46318</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>46318</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>46318</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>46276</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45526</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>45972</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46276</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45343</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>44943</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46317</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>45659</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>44735</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59055,7 +59055,7 @@
         <v>44981</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>45238</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45238</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45635</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>46275</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45995</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>46318</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>46144</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45237</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46150</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46149</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45590</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>45463</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>44994</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60112,7 +60112,7 @@
         <v>46153</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45541</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45541</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45573</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45280</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45894</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>44623</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45730</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>45254</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>44923</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45597</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61033,7 +61033,7 @@
         <v>45478</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>45618</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>44628</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>45238</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>44972</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>45636</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>45158</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44743</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45693</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45457</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>45149</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>44640</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45478</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45748</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45453</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45170</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
         <v>45656</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>44522</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45660</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45660</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>45297</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45238</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45238</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62792,7 +62792,7 @@
         <v>45238</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>45260</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62943,7 +62943,7 @@
         <v>45730</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45730</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>45232</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>44909</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>44903</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>45769</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>44628</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>45754</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63547,7 +63547,7 @@
         <v>44923</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>44564</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63693,7 +63693,7 @@
         <v>45152</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45239</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63839,7 +63839,7 @@
         <v>45546</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63912,7 +63912,7 @@
         <v>45481</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63990,7 +63990,7 @@
         <v>45226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>45190</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>45216</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64219,7 +64219,7 @@
         <v>45338</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>45048</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>45117</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45239</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64516,7 +64516,7 @@
         <v>45240</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64594,7 +64594,7 @@
         <v>45000</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64667,7 +64667,7 @@
         <v>45756</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64745,7 +64745,7 @@
         <v>44545</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64818,7 +64818,7 @@
         <v>44901</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64891,7 +64891,7 @@
         <v>45660</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>44847</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65037,7 +65037,7 @@
         <v>44914</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65115,7 +65115,7 @@
         <v>44637</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65188,7 +65188,7 @@
         <v>45575</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65266,7 +65266,7 @@
         <v>44942</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>44532</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65412,7 +65412,7 @@
         <v>44505</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65485,7 +65485,7 @@
         <v>45571</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65558,7 +65558,7 @@
         <v>45571</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65631,7 +65631,7 @@
         <v>45152</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65704,7 +65704,7 @@
         <v>45492</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65782,7 +65782,7 @@
         <v>45492</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65860,7 +65860,7 @@
         <v>44543</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65933,7 +65933,7 @@
         <v>45148</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66011,7 +66011,7 @@
         <v>44522</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44977</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>44977</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66245,7 +66245,7 @@
         <v>44963</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66323,7 +66323,7 @@
         <v>45524</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45161</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>45636</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66557,7 +66557,7 @@
         <v>45643</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66635,7 +66635,7 @@
         <v>45656</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>45399</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45114</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66864,7 +66864,7 @@
         <v>45748</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66937,7 +66937,7 @@
         <v>45579</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67010,7 +67010,7 @@
         <v>45555</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67083,7 +67083,7 @@
         <v>44515</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67156,7 +67156,7 @@
         <v>45161</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67234,7 +67234,7 @@
         <v>45516</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>45516</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>45232</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45582</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67541,7 +67541,7 @@
         <v>45376</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>45159</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>45485</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67760,7 +67760,7 @@
         <v>45048</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67833,7 +67833,7 @@
         <v>45349</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>45617</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67984,7 +67984,7 @@
         <v>45190</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68062,7 +68062,7 @@
         <v>45222</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68140,7 +68140,7 @@
         <v>45762</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68218,7 +68218,7 @@
         <v>45435</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>45216</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68374,7 +68374,7 @@
         <v>45429</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68452,7 +68452,7 @@
         <v>45222</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68530,7 +68530,7 @@
         <v>44615</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68603,7 +68603,7 @@
         <v>45148</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         <v>45225</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>45237</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>45254</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68910,7 +68910,7 @@
         <v>44747</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68988,7 +68988,7 @@
         <v>45092</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>45278</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69139,7 +69139,7 @@
         <v>45206</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>45408</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45469</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69368,7 +69368,7 @@
         <v>45202</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69446,7 +69446,7 @@
         <v>45756</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>45756</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69597,7 +69597,7 @@
         <v>45756</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69670,7 +69670,7 @@
         <v>44971</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69743,7 +69743,7 @@
         <v>45435</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69821,7 +69821,7 @@
         <v>45512</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69899,7 +69899,7 @@
         <v>45089</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69972,7 +69972,7 @@
         <v>44826</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70050,7 +70050,7 @@
         <v>45531</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>44657</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>45574</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70279,7 +70279,7 @@
         <v>44522</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70357,7 +70357,7 @@
         <v>45090</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>44540</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>45730</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70586,7 +70586,7 @@
         <v>45730</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70664,7 +70664,7 @@
         <v>45308</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70737,7 +70737,7 @@
         <v>45415</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70810,7 +70810,7 @@
         <v>45524</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>45597</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70966,7 +70966,7 @@
         <v>45574</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71039,7 +71039,7 @@
         <v>45390</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71117,7 +71117,7 @@
         <v>45495</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71195,7 +71195,7 @@
         <v>44627</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71268,7 +71268,7 @@
         <v>44748</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71346,7 +71346,7 @@
         <v>45378</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>45442</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>45526</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>44574</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>44566</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45061</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71794,7 +71794,7 @@
         <v>45393</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71867,7 +71867,7 @@
         <v>45061</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71940,7 +71940,7 @@
         <v>45393</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72013,7 +72013,7 @@
         <v>45061</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72086,7 +72086,7 @@
         <v>45393</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72159,7 +72159,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72237,7 +72237,7 @@
         <v>45932</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>

--- a/Översikt VILHELMINA.xlsx
+++ b/Översikt VILHELMINA.xlsx
@@ -601,7 +601,7 @@
         <v>44972</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         <v>45989</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>46104</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>44494</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>45558</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>45989</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>45636</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44644</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>44838</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44972</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45947</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>44494</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>46076</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46104</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>46104</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>45636</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>46141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45625</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>44881</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>44972</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46104</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>46104</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>45989</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45583</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46142</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>46276</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44972</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44522</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45561</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45295</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45716</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45989</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5402,7 +5402,7 @@
         <v>45636</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45478</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>45931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>46270</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>45054</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45399</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45113</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45509</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45764</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6536,7 +6536,7 @@
         <v>46258</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44945</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45887</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>45770</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45915</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>45636</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45149</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45051</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>45399</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>46073</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7776,7 +7776,7 @@
         <v>45636</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
         <v>45903</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>46265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>46265</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45208</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44657</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45399</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45636</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>45205</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>46097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>46275</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>45349</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44964</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44964</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45238</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>46058</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45463</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44732</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45644</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>46255</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45625</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44698</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45764</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45497</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>45490</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44888</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45478</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44648</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44515</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>45573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44972</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45665</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>46076</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45575</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45589</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>44664</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>45188</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45545</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>45709</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>45989</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>46009</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>46076</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45552</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46286</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45113</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44515</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45546</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>45957</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45961</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45545</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45278</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44806</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>46282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>46255</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45618</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>46080</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45461</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45558</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>45561</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45545</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>44806</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>45478</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45560</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46062</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>46093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>44529</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>45936</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>45730</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45399</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45487</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>44603</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45733</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45883</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45937</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45119</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>45625</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>45492</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>46003</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17568,7 +17568,7 @@
         <v>45751</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>46162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45560</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45636</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>46276</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45817</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46252</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45834</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18452,7 +18452,7 @@
         <v>46048</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45618</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46268</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>46273</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>45541</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46148</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45545</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45461</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>44518</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45643</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>44985</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>45895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>46093</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44518</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19996,7 +19996,7 @@
         <v>44532</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44911</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45541</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>46072</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20434,7 +20434,7 @@
         <v>46163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45936</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45399</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44494</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20873,7 +20873,7 @@
         <v>45117</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45523</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46181</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45515</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45736</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45205</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45540</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45586</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46210</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>46097</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45804</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45254</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45821</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>45874</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45582</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>45589</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45622</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>44560</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45573</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45240</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45206</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45526</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23719,7 +23719,7 @@
         <v>45105</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>44852</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23943,7 +23943,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>46247</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44812</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>44628</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>44619</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44619</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>44810</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>44867</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>44859</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>44533</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44628</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44844</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>44852</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44712</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44619</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44817</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44532</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44690</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44858</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>44743</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44743</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>44889</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>44754</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25871,7 +25871,7 @@
         <v>44619</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>44616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>44755</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>44532</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44743</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44743</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44852</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44743</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>44708</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>44532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44879</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>44799</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26870,7 +26870,7 @@
         <v>44617</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26948,7 +26948,7 @@
         <v>44545</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27021,7 +27021,7 @@
         <v>44495</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>44995</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>44837</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45883</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>44743</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27401,7 +27401,7 @@
         <v>44857</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45471</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45883</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45735</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44826</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27771,7 +27771,7 @@
         <v>45890</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>45890</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>45715</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45883</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28239,7 +28239,7 @@
         <v>45890</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28317,7 +28317,7 @@
         <v>45140</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28390,7 +28390,7 @@
         <v>45622</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         <v>45195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>45730</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28624,7 +28624,7 @@
         <v>45225</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28702,7 +28702,7 @@
         <v>45509</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44657</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>45166</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         <v>45000</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>44890</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29072,7 +29072,7 @@
         <v>45884</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45775</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44881</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45428</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45042</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45884</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45884</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>46157</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45653</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45403</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29832,7 +29832,7 @@
         <v>44545</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>46162</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>46048</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30129,7 +30129,7 @@
         <v>45993</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45558</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>44545</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>45915</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46163</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45478</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>45636</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30655,7 +30655,7 @@
         <v>45915</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30728,7 +30728,7 @@
         <v>46163</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30806,7 +30806,7 @@
         <v>46168</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>44943</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30957,7 +30957,7 @@
         <v>45470</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31035,7 +31035,7 @@
         <v>45089</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31186,7 +31186,7 @@
         <v>45757</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>46168</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45154</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>45331</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31483,7 +31483,7 @@
         <v>46171</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31556,7 +31556,7 @@
         <v>45000</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>46174</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>44963</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44515</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>46175</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45469</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>46087</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>44972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32160,7 +32160,7 @@
         <v>45236</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45937</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>44847</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32389,7 +32389,7 @@
         <v>44847</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45436</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>44859</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>45399</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>44972</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         <v>44972</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>46174</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32993,7 +32993,7 @@
         <v>45154</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>44802</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>45944</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>44847</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45636</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45636</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45636</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>45625</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>45944</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45239</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45419</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45450</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45188</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>44855</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45232</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45377</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45443</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45453</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45453</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34450,7 +34450,7 @@
         <v>45526</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34528,7 +34528,7 @@
         <v>45526</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45951</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45951</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34830,7 +34830,7 @@
         <v>45125</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45951</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34976,7 +34976,7 @@
         <v>46183</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>46183</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46183</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>45649</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>45957</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35356,7 +35356,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45954</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45957</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45558</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45957</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45957</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>46189</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>45957</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45957</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45957</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45957</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45957</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45957</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45508</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46191</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>46191</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36617,7 +36617,7 @@
         <v>45236</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>45475</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>46184</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45195</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45636</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45442</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45743</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>45971</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45229</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>46196</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37387,7 +37387,7 @@
         <v>46196</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>46199</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>46198</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46198</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46198</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37767,7 +37767,7 @@
         <v>46199</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>44977</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>44658</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45625</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45709</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46198</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45147</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45730</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45730</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45979</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45982</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45259</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45516</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45981</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>45362</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38902,7 +38902,7 @@
         <v>45642</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>44972</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>46205</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45463</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>46204</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>46204</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39365,7 +39365,7 @@
         <v>46205</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39438,7 +39438,7 @@
         <v>45985</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>46204</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>46204</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>46205</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39745,7 +39745,7 @@
         <v>45985</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>46204</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39896,7 +39896,7 @@
         <v>46205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39969,7 +39969,7 @@
         <v>46209</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -40047,7 +40047,7 @@
         <v>46209</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>46206</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40203,7 +40203,7 @@
         <v>45769</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>44889</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>46209</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>46209</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45756</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40583,7 +40583,7 @@
         <v>46206</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40661,7 +40661,7 @@
         <v>46076</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40734,7 +40734,7 @@
         <v>45526</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>46209</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40890,7 +40890,7 @@
         <v>45142</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>46210</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45672</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -41114,7 +41114,7 @@
         <v>45762</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41192,7 +41192,7 @@
         <v>45876</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41265,7 +41265,7 @@
         <v>46210</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41338,7 +41338,7 @@
         <v>44972</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45565</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>45996</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>45643</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>46217</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         <v>45999</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41864,7 +41864,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41937,7 +41937,7 @@
         <v>46213</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44881</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -42083,7 +42083,7 @@
         <v>45225</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -42161,7 +42161,7 @@
         <v>44686</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>46213</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42312,7 +42312,7 @@
         <v>45622</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42385,7 +42385,7 @@
         <v>45953</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>46001</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42536,7 +42536,7 @@
         <v>45278</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42614,7 +42614,7 @@
         <v>45478</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45777</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>44949</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>45779</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46006</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45216</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>45140</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>44852</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>46282</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43296,7 +43296,7 @@
         <v>46282</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45989</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43452,7 +43452,7 @@
         <v>45989</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>45989</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43608,7 +43608,7 @@
         <v>45989</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45989</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43764,7 +43764,7 @@
         <v>46085</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43837,7 +43837,7 @@
         <v>46097</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43910,7 +43910,7 @@
         <v>46281</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43983,7 +43983,7 @@
         <v>46163</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -44056,7 +44056,7 @@
         <v>45548</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>45792</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45791</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45552</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44368,7 +44368,7 @@
         <v>45433</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44441,7 +44441,7 @@
         <v>45786</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45786</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>46283</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44660,7 +44660,7 @@
         <v>45147</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>46038</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45793</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45518</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45636</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45149</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -45128,7 +45128,7 @@
         <v>45813</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>45996</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>46244</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45357,7 +45357,7 @@
         <v>45415</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>46045</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>46286</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45591,7 +45591,7 @@
         <v>45800</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45669,7 +45669,7 @@
         <v>46076</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45742,7 +45742,7 @@
         <v>45800</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         <v>44847</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45893,7 +45893,7 @@
         <v>45799</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>46289</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>46157</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -46122,7 +46122,7 @@
         <v>46048</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -46195,7 +46195,7 @@
         <v>45803</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>46289</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45545</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45804</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46575,7 +46575,7 @@
         <v>46055</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>46289</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45805</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46799,7 +46799,7 @@
         <v>45096</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46872,7 +46872,7 @@
         <v>45636</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46950,7 +46950,7 @@
         <v>45440</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>46055</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>46055</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44978</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47242,7 +47242,7 @@
         <v>46055</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45810</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45810</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>46049</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47544,7 +47544,7 @@
         <v>45625</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>46066</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47700,7 +47700,7 @@
         <v>45659</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45659</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45817</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         <v>45659</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>46070</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45300</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>46248</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -48221,7 +48221,7 @@
         <v>45817</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>44686</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45820</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>46162</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45238</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48606,7 +48606,7 @@
         <v>45824</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         <v>45824</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45989</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>46252</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>46252</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
         <v>46252</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>46252</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45831</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>46252</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49283,7 +49283,7 @@
         <v>46252</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49356,7 +49356,7 @@
         <v>46255</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49429,7 +49429,7 @@
         <v>46255</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49502,7 +49502,7 @@
         <v>45834</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>45833</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>46255</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49726,7 +49726,7 @@
         <v>46255</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49799,7 +49799,7 @@
         <v>45791</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49877,7 +49877,7 @@
         <v>45840</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49950,7 +49950,7 @@
         <v>46093</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45232</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>46255</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -50174,7 +50174,7 @@
         <v>45161</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45777</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>46255</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45841</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50476,7 +50476,7 @@
         <v>46255</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>46255</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50695,7 +50695,7 @@
         <v>46252</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>46301</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>46105</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50924,7 +50924,7 @@
         <v>45847</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>46301</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>46301</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>46258</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -51236,7 +51236,7 @@
         <v>46301</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>46301</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>44972</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46301</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>46301</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>45853</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51694,7 +51694,7 @@
         <v>46301</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51767,7 +51767,7 @@
         <v>45853</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51845,7 +51845,7 @@
         <v>45483</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51923,7 +51923,7 @@
         <v>45205</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -52001,7 +52001,7 @@
         <v>45534</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -52079,7 +52079,7 @@
         <v>46111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -52157,7 +52157,7 @@
         <v>46111</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>46113</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52313,7 +52313,7 @@
         <v>46301</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>45862</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52464,7 +52464,7 @@
         <v>46113</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52542,7 +52542,7 @@
         <v>46304</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45511</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>46113</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>46304</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>45246</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52922,7 +52922,7 @@
         <v>45545</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52995,7 +52995,7 @@
         <v>46121</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -53073,7 +53073,7 @@
         <v>46304</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -53146,7 +53146,7 @@
         <v>45874</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>46125</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -53302,7 +53302,7 @@
         <v>46122</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>46122</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53448,7 +53448,7 @@
         <v>46122</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         <v>45099</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53599,7 +53599,7 @@
         <v>45874</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53677,7 +53677,7 @@
         <v>45874</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45877</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>44515</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>44515</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45877</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -54057,7 +54057,7 @@
         <v>46129</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -54135,7 +54135,7 @@
         <v>46132</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -54213,7 +54213,7 @@
         <v>45443</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -54291,7 +54291,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>46132</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>44972</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54525,7 +54525,7 @@
         <v>44911</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54603,7 +54603,7 @@
         <v>45734</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54676,7 +54676,7 @@
         <v>45883</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>46183</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54827,7 +54827,7 @@
         <v>45541</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45545</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54983,7 +54983,7 @@
         <v>45316</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -55061,7 +55061,7 @@
         <v>45560</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -55139,7 +55139,7 @@
         <v>45205</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -55217,7 +55217,7 @@
         <v>45206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -55295,7 +55295,7 @@
         <v>45207</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -55373,7 +55373,7 @@
         <v>45216</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55451,7 +55451,7 @@
         <v>46262</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55529,7 +55529,7 @@
         <v>45800</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55607,7 +55607,7 @@
         <v>45586</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>45587</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55763,7 +55763,7 @@
         <v>46178</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>45589</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45587</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46129</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>44903</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>45388</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45518</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -56299,7 +56299,7 @@
         <v>45518</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>46267</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>44917</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45583</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56606,7 +56606,7 @@
         <v>45408</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56679,7 +56679,7 @@
         <v>45847</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>46314</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45692</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56908,7 +56908,7 @@
         <v>45586</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56986,7 +56986,7 @@
         <v>45251</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45505</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45757</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45993</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>44568</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45912</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45709</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>44957</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>45992</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45979</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>46272</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46315</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>46273</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57945,7 +57945,7 @@
         <v>44693</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>46318</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -58091,7 +58091,7 @@
         <v>45972</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -58164,7 +58164,7 @@
         <v>46318</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -58237,7 +58237,7 @@
         <v>46318</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>46318</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -58383,7 +58383,7 @@
         <v>46276</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58456,7 +58456,7 @@
         <v>45526</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58534,7 +58534,7 @@
         <v>45972</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58607,7 +58607,7 @@
         <v>46276</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58680,7 +58680,7 @@
         <v>45343</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58753,7 +58753,7 @@
         <v>44943</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>46317</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58899,7 +58899,7 @@
         <v>45659</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>44735</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -59055,7 +59055,7 @@
         <v>44981</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -59128,7 +59128,7 @@
         <v>45238</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -59206,7 +59206,7 @@
         <v>45238</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45635</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -59357,7 +59357,7 @@
         <v>46275</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59435,7 +59435,7 @@
         <v>45995</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59508,7 +59508,7 @@
         <v>46318</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59581,7 +59581,7 @@
         <v>46144</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45237</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>46150</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46149</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45590</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59956,7 +59956,7 @@
         <v>45463</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>44994</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -60112,7 +60112,7 @@
         <v>46153</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -60190,7 +60190,7 @@
         <v>45541</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45541</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -60346,7 +60346,7 @@
         <v>45573</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -60419,7 +60419,7 @@
         <v>45280</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60492,7 +60492,7 @@
         <v>45894</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>45084</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>44623</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45730</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>45254</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60877,7 +60877,7 @@
         <v>44923</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>45597</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -61033,7 +61033,7 @@
         <v>45478</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -61111,7 +61111,7 @@
         <v>45618</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -61189,7 +61189,7 @@
         <v>44628</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -61262,7 +61262,7 @@
         <v>45238</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -61340,7 +61340,7 @@
         <v>44972</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -61418,7 +61418,7 @@
         <v>45636</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61496,7 +61496,7 @@
         <v>45158</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61569,7 +61569,7 @@
         <v>44743</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61647,7 +61647,7 @@
         <v>45693</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61725,7 +61725,7 @@
         <v>45457</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61803,7 +61803,7 @@
         <v>45149</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61881,7 +61881,7 @@
         <v>44640</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61954,7 +61954,7 @@
         <v>45478</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45748</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45453</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45170</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -62261,7 +62261,7 @@
         <v>45656</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -62339,7 +62339,7 @@
         <v>44522</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -62417,7 +62417,7 @@
         <v>45660</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45660</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62563,7 +62563,7 @@
         <v>45297</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45238</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62714,7 +62714,7 @@
         <v>45238</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62792,7 +62792,7 @@
         <v>45238</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>45260</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62943,7 +62943,7 @@
         <v>45730</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>45730</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -63099,7 +63099,7 @@
         <v>45232</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -63172,7 +63172,7 @@
         <v>44909</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>44903</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -63318,7 +63318,7 @@
         <v>45769</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -63396,7 +63396,7 @@
         <v>44628</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -63469,7 +63469,7 @@
         <v>45754</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63547,7 +63547,7 @@
         <v>44923</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>44564</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63693,7 +63693,7 @@
         <v>45152</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>45239</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63839,7 +63839,7 @@
         <v>45546</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63912,7 +63912,7 @@
         <v>45481</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63990,7 +63990,7 @@
         <v>45226</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -64068,7 +64068,7 @@
         <v>45190</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -64141,7 +64141,7 @@
         <v>45216</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -64219,7 +64219,7 @@
         <v>45338</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -64292,7 +64292,7 @@
         <v>45048</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -64365,7 +64365,7 @@
         <v>45117</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -64443,7 +64443,7 @@
         <v>45239</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64516,7 +64516,7 @@
         <v>45240</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64594,7 +64594,7 @@
         <v>45000</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64667,7 +64667,7 @@
         <v>45756</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64745,7 +64745,7 @@
         <v>44545</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64818,7 +64818,7 @@
         <v>44901</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64891,7 +64891,7 @@
         <v>45660</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>44847</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -65037,7 +65037,7 @@
         <v>44914</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -65115,7 +65115,7 @@
         <v>44637</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -65188,7 +65188,7 @@
         <v>45575</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -65266,7 +65266,7 @@
         <v>44942</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -65339,7 +65339,7 @@
         <v>44532</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -65412,7 +65412,7 @@
         <v>44505</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65485,7 +65485,7 @@
         <v>45571</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65558,7 +65558,7 @@
         <v>45571</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65631,7 +65631,7 @@
         <v>45152</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65704,7 +65704,7 @@
         <v>45492</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65782,7 +65782,7 @@
         <v>45492</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65860,7 +65860,7 @@
         <v>44543</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65933,7 +65933,7 @@
         <v>45148</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -66011,7 +66011,7 @@
         <v>44522</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -66089,7 +66089,7 @@
         <v>44977</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -66167,7 +66167,7 @@
         <v>44977</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -66245,7 +66245,7 @@
         <v>44963</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -66323,7 +66323,7 @@
         <v>45524</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -66401,7 +66401,7 @@
         <v>45161</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -66479,7 +66479,7 @@
         <v>45636</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66557,7 +66557,7 @@
         <v>45643</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66635,7 +66635,7 @@
         <v>45656</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66713,7 +66713,7 @@
         <v>45399</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66786,7 +66786,7 @@
         <v>45114</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66864,7 +66864,7 @@
         <v>45748</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66937,7 +66937,7 @@
         <v>45579</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -67010,7 +67010,7 @@
         <v>45555</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -67083,7 +67083,7 @@
         <v>44515</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -67156,7 +67156,7 @@
         <v>45161</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -67234,7 +67234,7 @@
         <v>45516</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -67312,7 +67312,7 @@
         <v>45516</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         <v>45232</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -67463,7 +67463,7 @@
         <v>45582</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67541,7 +67541,7 @@
         <v>45376</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67614,7 +67614,7 @@
         <v>45159</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67687,7 +67687,7 @@
         <v>45485</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67760,7 +67760,7 @@
         <v>45048</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67833,7 +67833,7 @@
         <v>45349</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67906,7 +67906,7 @@
         <v>45617</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67984,7 +67984,7 @@
         <v>45190</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -68062,7 +68062,7 @@
         <v>45222</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -68140,7 +68140,7 @@
         <v>45762</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -68218,7 +68218,7 @@
         <v>45435</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -68296,7 +68296,7 @@
         <v>45216</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -68374,7 +68374,7 @@
         <v>45429</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -68452,7 +68452,7 @@
         <v>45222</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -68530,7 +68530,7 @@
         <v>44615</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68603,7 +68603,7 @@
         <v>45148</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         <v>45225</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68759,7 +68759,7 @@
         <v>45237</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68837,7 +68837,7 @@
         <v>45254</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68910,7 +68910,7 @@
         <v>44747</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68988,7 +68988,7 @@
         <v>45092</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         <v>45278</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -69139,7 +69139,7 @@
         <v>45206</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -69217,7 +69217,7 @@
         <v>45408</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -69290,7 +69290,7 @@
         <v>45469</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -69368,7 +69368,7 @@
         <v>45202</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -69446,7 +69446,7 @@
         <v>45756</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -69524,7 +69524,7 @@
         <v>45756</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69597,7 +69597,7 @@
         <v>45756</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69670,7 +69670,7 @@
         <v>44971</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69743,7 +69743,7 @@
         <v>45435</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69821,7 +69821,7 @@
         <v>45512</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69899,7 +69899,7 @@
         <v>45089</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69972,7 +69972,7 @@
         <v>44826</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -70050,7 +70050,7 @@
         <v>45531</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -70128,7 +70128,7 @@
         <v>44657</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -70201,7 +70201,7 @@
         <v>45574</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -70279,7 +70279,7 @@
         <v>44522</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -70357,7 +70357,7 @@
         <v>45090</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -70435,7 +70435,7 @@
         <v>44540</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -70508,7 +70508,7 @@
         <v>45730</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70586,7 +70586,7 @@
         <v>45730</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70664,7 +70664,7 @@
         <v>45308</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70737,7 +70737,7 @@
         <v>45415</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70810,7 +70810,7 @@
         <v>45524</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70888,7 +70888,7 @@
         <v>45597</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70966,7 +70966,7 @@
         <v>45574</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -71039,7 +71039,7 @@
         <v>45390</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -71117,7 +71117,7 @@
         <v>45495</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -71195,7 +71195,7 @@
         <v>44627</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -71268,7 +71268,7 @@
         <v>44748</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -71346,7 +71346,7 @@
         <v>45378</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -71419,7 +71419,7 @@
         <v>45442</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -71497,7 +71497,7 @@
         <v>45526</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         <v>44574</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71648,7 +71648,7 @@
         <v>44566</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71721,7 +71721,7 @@
         <v>45061</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71794,7 +71794,7 @@
         <v>45393</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71867,7 +71867,7 @@
         <v>45061</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71940,7 +71940,7 @@
         <v>45393</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -72013,7 +72013,7 @@
         <v>45061</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -72086,7 +72086,7 @@
         <v>45393</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -72159,7 +72159,7 @@
         <v>45748</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -72237,7 +72237,7 @@
         <v>45932</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
